--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X9.cis.beta.carotene/RANDOMSEARCH_DETAILS_X9.cis.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X9.cis.beta.carotene/RANDOMSEARCH_DETAILS_X9.cis.beta.carotene.xlsx
@@ -469,17 +469,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9554</v>
+        <v>0.9559</v>
       </c>
       <c r="F2" t="n">
-        <v>20.2734</v>
+        <v>20.1046</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>41.4024</v>
       </c>
     </row>
     <row r="3">
@@ -498,17 +498,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.956</v>
+        <v>0.9699</v>
       </c>
       <c r="F3" t="n">
-        <v>20.3218</v>
+        <v>17.1809</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>41.1195</v>
       </c>
     </row>
     <row r="4">
@@ -527,17 +527,17 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9267</v>
+        <v>0.9265</v>
       </c>
       <c r="F4" t="n">
-        <v>25.6435</v>
+        <v>25.6773</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>43.7205</v>
       </c>
     </row>
     <row r="5">
@@ -556,17 +556,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8626</v>
+        <v>0.8629</v>
       </c>
       <c r="F5" t="n">
-        <v>36.9123</v>
+        <v>36.8947</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>58.2762</v>
       </c>
     </row>
     <row r="6">
@@ -585,17 +585,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8615</v>
+        <v>0.9414</v>
       </c>
       <c r="F6" t="n">
-        <v>36.7879</v>
+        <v>26.7918</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>57.8911</v>
       </c>
     </row>
     <row r="7">
@@ -614,7 +614,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -624,7 +624,7 @@
         <v>24.3001</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>43.2339</v>
       </c>
     </row>
     <row r="8">
@@ -643,17 +643,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9565</v>
+        <v>0.9633</v>
       </c>
       <c r="F8" t="n">
-        <v>20.2513</v>
+        <v>18.9322</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>44.7461</v>
       </c>
     </row>
     <row r="9">
@@ -672,17 +672,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9447</v>
       </c>
       <c r="F9" t="n">
-        <v>20.7969</v>
+        <v>23.1559</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>41.3857</v>
       </c>
     </row>
     <row r="10">
@@ -701,17 +701,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9577</v>
+        <v>0.9626</v>
       </c>
       <c r="F10" t="n">
-        <v>19.9451</v>
+        <v>19.0434</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>44.8206</v>
       </c>
     </row>
     <row r="11">
@@ -730,17 +730,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9578</v>
+        <v>0.9576</v>
       </c>
       <c r="F11" t="n">
-        <v>19.8887</v>
+        <v>19.9166</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>44.6816</v>
       </c>
     </row>
     <row r="12">
@@ -759,17 +759,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9573</v>
       </c>
       <c r="F12" t="n">
-        <v>19.9452</v>
+        <v>19.9448</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>44.5388</v>
       </c>
     </row>
     <row r="13">
@@ -788,17 +788,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9572000000000001</v>
+        <v>0.9631</v>
       </c>
       <c r="F13" t="n">
-        <v>19.8524</v>
+        <v>18.8356</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>43.8248</v>
       </c>
     </row>
     <row r="14">
@@ -817,17 +817,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9584</v>
+        <v>0.9391</v>
       </c>
       <c r="F14" t="n">
-        <v>19.8072</v>
+        <v>23.4291</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>44.842</v>
       </c>
     </row>
     <row r="15">
@@ -846,17 +846,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>0.9573</v>
       </c>
       <c r="F15" t="n">
-        <v>19.9536</v>
+        <v>19.9497</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>44.5383</v>
       </c>
     </row>
     <row r="16">
@@ -875,17 +875,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9568</v>
+        <v>0.9564</v>
       </c>
       <c r="F16" t="n">
-        <v>20.0788</v>
+        <v>20.1341</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>44.3105</v>
       </c>
     </row>
     <row r="17">
@@ -904,17 +904,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9631</v>
+        <v>0.9629</v>
       </c>
       <c r="F17" t="n">
-        <v>18.8678</v>
+        <v>18.9246</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>43.8365</v>
       </c>
     </row>
     <row r="18">
@@ -933,17 +933,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9349</v>
+        <v>0.9352</v>
       </c>
       <c r="F18" t="n">
-        <v>24.3947</v>
+        <v>24.3446</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>41.3663</v>
       </c>
     </row>
     <row r="19">
@@ -962,17 +962,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9338</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>24.5359</v>
+        <v>24.5113</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>41.6025</v>
       </c>
     </row>
     <row r="20">
@@ -991,17 +991,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9216</v>
+        <v>0.9215</v>
       </c>
       <c r="F20" t="n">
-        <v>26.6559</v>
+        <v>26.665</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>41.8334</v>
       </c>
     </row>
     <row r="21">
@@ -1020,17 +1020,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9203</v>
+        <v>0.9206</v>
       </c>
       <c r="F21" t="n">
-        <v>26.7925</v>
+        <v>26.7647</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>41.7354</v>
       </c>
     </row>
     <row r="22">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9588</v>
+        <v>0.9565</v>
       </c>
       <c r="F22" t="n">
-        <v>20.0248</v>
+        <v>20.5006</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>41.6238</v>
       </c>
     </row>
     <row r="23">
@@ -1078,17 +1078,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9364</v>
+        <v>0.9365</v>
       </c>
       <c r="F23" t="n">
-        <v>23.5747</v>
+        <v>23.5494</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>41.8873</v>
       </c>
     </row>
     <row r="24">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9298999999999999</v>
+        <v>0.9302</v>
       </c>
       <c r="F24" t="n">
-        <v>25.0818</v>
+        <v>25.0567</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>41.8984</v>
       </c>
     </row>
     <row r="25">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9376</v>
+        <v>0.9192</v>
       </c>
       <c r="F25" t="n">
-        <v>23.4332</v>
+        <v>26.9596</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>42.2101</v>
       </c>
     </row>
     <row r="26">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.9499</v>
+        <v>0.95</v>
       </c>
       <c r="F26" t="n">
-        <v>21.4166</v>
+        <v>21.374</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>41.5208</v>
       </c>
     </row>
     <row r="27">
@@ -1194,17 +1194,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9446</v>
+        <v>0.9294</v>
       </c>
       <c r="F27" t="n">
-        <v>22.2819</v>
+        <v>25.5904</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>41.7723</v>
       </c>
     </row>
     <row r="28">
@@ -1223,17 +1223,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9461000000000001</v>
+        <v>0.9464</v>
       </c>
       <c r="F28" t="n">
-        <v>21.8976</v>
+        <v>21.8518</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>41.7148</v>
       </c>
     </row>
     <row r="29">
@@ -1252,17 +1252,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9335</v>
+        <v>0.9338</v>
       </c>
       <c r="F29" t="n">
-        <v>24.5243</v>
+        <v>24.4841</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>41.8887</v>
       </c>
     </row>
     <row r="30">
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9581</v>
+        <v>0.9584</v>
       </c>
       <c r="F30" t="n">
-        <v>20.424</v>
+        <v>20.3849</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>41.921</v>
       </c>
     </row>
     <row r="31">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9207</v>
+        <v>0.9206</v>
       </c>
       <c r="F31" t="n">
-        <v>26.8076</v>
+        <v>26.8066</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>41.604</v>
       </c>
     </row>
     <row r="32">
@@ -1339,17 +1339,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9137</v>
+        <v>0.9137999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>27.9003</v>
+        <v>27.8922</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>41.933</v>
       </c>
     </row>
     <row r="33">
@@ -1368,17 +1368,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9575</v>
+        <v>0.9577</v>
       </c>
       <c r="F33" t="n">
-        <v>20.4036</v>
+        <v>20.3422</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>41.736</v>
       </c>
     </row>
     <row r="34">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.972</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>16.6102</v>
+        <v>16.5521</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>40.3146</v>
       </c>
     </row>
     <row r="35">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9462</v>
+        <v>0.9467</v>
       </c>
       <c r="F35" t="n">
-        <v>22.9499</v>
+        <v>22.8522</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>40.6447</v>
       </c>
     </row>
     <row r="36">
@@ -1455,17 +1455,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9454</v>
+        <v>0.9455</v>
       </c>
       <c r="F36" t="n">
-        <v>23.1113</v>
+        <v>23.0929</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>40.4369</v>
       </c>
     </row>
     <row r="37">
@@ -1484,17 +1484,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>0.9473</v>
       </c>
       <c r="F37" t="n">
-        <v>22.4629</v>
+        <v>22.4584</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>39.9443</v>
       </c>
     </row>
     <row r="38">
@@ -1513,17 +1513,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9436</v>
+        <v>0.9435</v>
       </c>
       <c r="F38" t="n">
-        <v>22.972</v>
+        <v>23.0092</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>40.1105</v>
       </c>
     </row>
     <row r="39">
@@ -1542,17 +1542,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
         <v>0.9432</v>
       </c>
       <c r="F39" t="n">
-        <v>22.7928</v>
+        <v>22.7951</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>40.2315</v>
       </c>
     </row>
     <row r="40">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.946</v>
+        <v>0.945</v>
       </c>
       <c r="F40" t="n">
-        <v>22.3131</v>
+        <v>22.6186</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>40.309</v>
       </c>
     </row>
     <row r="41">
@@ -1600,17 +1600,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9443</v>
+        <v>0.9726</v>
       </c>
       <c r="F41" t="n">
-        <v>23.4586</v>
+        <v>16.4738</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>40.3897</v>
       </c>
     </row>
     <row r="42">
@@ -1629,17 +1629,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9462</v>
+        <v>0.9466</v>
       </c>
       <c r="F42" t="n">
-        <v>22.943</v>
+        <v>22.8697</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>40.8133</v>
       </c>
     </row>
     <row r="43">
@@ -1658,17 +1658,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9448</v>
+        <v>0.9447</v>
       </c>
       <c r="F43" t="n">
-        <v>23.2659</v>
+        <v>23.2662</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>40.6573</v>
       </c>
     </row>
     <row r="44">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9474</v>
+        <v>0.9475</v>
       </c>
       <c r="F44" t="n">
-        <v>22.4786</v>
+        <v>22.4681</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>39.9893</v>
       </c>
     </row>
     <row r="45">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9445</v>
+        <v>0.9446</v>
       </c>
       <c r="F45" t="n">
-        <v>22.8918</v>
+        <v>22.9149</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>39.4668</v>
       </c>
     </row>
     <row r="46">
@@ -1745,17 +1745,17 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9445</v>
+        <v>0.9444</v>
       </c>
       <c r="F46" t="n">
-        <v>22.6154</v>
+        <v>22.6427</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>40.3507</v>
       </c>
     </row>
     <row r="47">
@@ -1774,17 +1774,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9458</v>
+        <v>0.9449</v>
       </c>
       <c r="F47" t="n">
-        <v>22.3264</v>
+        <v>22.6568</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>40.673</v>
       </c>
     </row>
     <row r="48">
@@ -1803,17 +1803,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9434</v>
+        <v>0.9432</v>
       </c>
       <c r="F48" t="n">
-        <v>23.0539</v>
+        <v>23.0784</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>41.115</v>
       </c>
     </row>
     <row r="49">
@@ -1832,17 +1832,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.9535</v>
+        <v>0.953</v>
       </c>
       <c r="F49" t="n">
-        <v>20.7412</v>
+        <v>20.8611</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>40.3967</v>
       </c>
     </row>
     <row r="50">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.8917</v>
+        <v>0.8914</v>
       </c>
       <c r="F50" t="n">
-        <v>34.7834</v>
+        <v>34.8317</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>57.6922</v>
       </c>
     </row>
     <row r="51">
@@ -1890,17 +1890,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>0.8639</v>
       </c>
       <c r="F51" t="n">
-        <v>37.6676</v>
+        <v>37.6518</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>57.3137</v>
       </c>
     </row>
     <row r="52">
@@ -1919,17 +1919,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8373</v>
+        <v>0.8369</v>
       </c>
       <c r="F52" t="n">
-        <v>39.759</v>
+        <v>39.7738</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>57.0967</v>
       </c>
     </row>
     <row r="53">
@@ -1948,17 +1948,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8892</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="F53" t="n">
-        <v>35.1889</v>
+        <v>37.5511</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>56.7012</v>
       </c>
     </row>
     <row r="54">
@@ -1977,17 +1977,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8714</v>
+        <v>0.8713</v>
       </c>
       <c r="F54" t="n">
-        <v>36.5768</v>
+        <v>36.5813</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>55.8172</v>
       </c>
     </row>
     <row r="55">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>0.8538</v>
       </c>
       <c r="F55" t="n">
-        <v>37.9853</v>
+        <v>37.992</v>
       </c>
       <c r="G55" t="n">
-        <v>0</v>
+        <v>57.5836</v>
       </c>
     </row>
     <row r="56">
@@ -2035,17 +2035,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8612</v>
+        <v>0.8615</v>
       </c>
       <c r="F56" t="n">
-        <v>37.9159</v>
+        <v>37.9013</v>
       </c>
       <c r="G56" t="n">
-        <v>0</v>
+        <v>57.0436</v>
       </c>
     </row>
     <row r="57">
@@ -2064,17 +2064,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.8641</v>
+        <v>0.864</v>
       </c>
       <c r="F57" t="n">
-        <v>37.6309</v>
+        <v>37.631</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>56.6254</v>
       </c>
     </row>
     <row r="58">
@@ -2093,17 +2093,17 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9374</v>
+        <v>0.9408</v>
       </c>
       <c r="F58" t="n">
-        <v>26.9453</v>
+        <v>26.9446</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>57.8834</v>
       </c>
     </row>
     <row r="59">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9357</v>
+        <v>0.9358</v>
       </c>
       <c r="F59" t="n">
-        <v>27.1607</v>
+        <v>27.1568</v>
       </c>
       <c r="G59" t="n">
-        <v>0</v>
+        <v>57.8704</v>
       </c>
     </row>
     <row r="60">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9362</v>
+        <v>0.9365</v>
       </c>
       <c r="F60" t="n">
-        <v>27.0438</v>
+        <v>27.0186</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>57.876</v>
       </c>
     </row>
     <row r="61">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>0.9396</v>
       </c>
       <c r="F61" t="n">
-        <v>27.0319</v>
+        <v>27.0022</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>57.8034</v>
       </c>
     </row>
     <row r="62">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8414</v>
+        <v>0.8415</v>
       </c>
       <c r="F62" t="n">
-        <v>38.5568</v>
+        <v>38.5502</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>58.1883</v>
       </c>
     </row>
     <row r="63">
@@ -2238,17 +2238,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8605</v>
+        <v>0.8608</v>
       </c>
       <c r="F63" t="n">
-        <v>36.6197</v>
+        <v>36.5895</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>58.1783</v>
       </c>
     </row>
     <row r="64">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8696</v>
+        <v>0.8692</v>
       </c>
       <c r="F64" t="n">
-        <v>36.1269</v>
+        <v>36.1385</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>58.1433</v>
       </c>
     </row>
     <row r="65">
@@ -2296,17 +2296,17 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8609</v>
+        <v>0.8613</v>
       </c>
       <c r="F65" t="n">
-        <v>36.8119</v>
+        <v>36.7981</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>58.0509</v>
       </c>
     </row>
     <row r="66">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8925999999999999</v>
+        <v>0.8915</v>
       </c>
       <c r="F66" t="n">
-        <v>34.2483</v>
+        <v>34.3183</v>
       </c>
       <c r="G66" t="n">
-        <v>0</v>
+        <v>56.6655</v>
       </c>
     </row>
     <row r="67">
@@ -2354,17 +2354,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8576</v>
+        <v>0.8774</v>
       </c>
       <c r="F67" t="n">
-        <v>38.0212</v>
+        <v>36.1072</v>
       </c>
       <c r="G67" t="n">
-        <v>0</v>
+        <v>56.9639</v>
       </c>
     </row>
     <row r="68">
@@ -2383,17 +2383,17 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9126</v>
+        <v>0.9131</v>
       </c>
       <c r="F68" t="n">
-        <v>31.0999</v>
+        <v>31.0511</v>
       </c>
       <c r="G68" t="n">
-        <v>0</v>
+        <v>56.8406</v>
       </c>
     </row>
     <row r="69">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9326</v>
+        <v>0.9555</v>
       </c>
       <c r="F69" t="n">
-        <v>24.7438</v>
+        <v>20.6827</v>
       </c>
       <c r="G69" t="n">
-        <v>0</v>
+        <v>43.0133</v>
       </c>
     </row>
     <row r="70">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.931</v>
+        <v>0.9311</v>
       </c>
       <c r="F70" t="n">
-        <v>24.8311</v>
+        <v>24.8029</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>42.7936</v>
       </c>
     </row>
     <row r="71">
@@ -2470,17 +2470,17 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9515</v>
+        <v>0.9752999999999999</v>
       </c>
       <c r="F71" t="n">
-        <v>21.0472</v>
+        <v>15.3741</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>43.1087</v>
       </c>
     </row>
     <row r="72">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9308</v>
+        <v>0.9498</v>
       </c>
       <c r="F72" t="n">
-        <v>24.7698</v>
+        <v>21.3599</v>
       </c>
       <c r="G72" t="n">
-        <v>0</v>
+        <v>43.1493</v>
       </c>
     </row>
     <row r="73">
@@ -2528,17 +2528,17 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9671</v>
+        <v>0.9673</v>
       </c>
       <c r="F73" t="n">
-        <v>18.7142</v>
+        <v>18.6537</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>43.7181</v>
       </c>
     </row>
     <row r="74">
@@ -2557,17 +2557,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E74" t="n">
         <v>0.9366</v>
       </c>
       <c r="F74" t="n">
-        <v>24.584</v>
+        <v>24.5659</v>
       </c>
       <c r="G74" t="n">
-        <v>0</v>
+        <v>43.5693</v>
       </c>
     </row>
     <row r="75">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9318</v>
+        <v>0.9305</v>
       </c>
       <c r="F75" t="n">
-        <v>24.5519</v>
+        <v>24.7148</v>
       </c>
       <c r="G75" t="n">
-        <v>0</v>
+        <v>44.2871</v>
       </c>
     </row>
     <row r="76">
@@ -2615,17 +2615,17 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9318</v>
+        <v>0.9305</v>
       </c>
       <c r="F76" t="n">
-        <v>24.5519</v>
+        <v>24.7148</v>
       </c>
       <c r="G76" t="n">
-        <v>0</v>
+        <v>44.2871</v>
       </c>
     </row>
     <row r="77">
@@ -2644,17 +2644,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8702</v>
+        <v>0.8699</v>
       </c>
       <c r="F77" t="n">
-        <v>35.984</v>
+        <v>36.0165</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>57.6014</v>
       </c>
     </row>
     <row r="78">
@@ -2673,17 +2673,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8812</v>
+        <v>0.8809</v>
       </c>
       <c r="F78" t="n">
-        <v>34.2591</v>
+        <v>34.2671</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>57.4587</v>
       </c>
     </row>
     <row r="79">
@@ -2702,17 +2702,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.8791</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F79" t="n">
-        <v>34.3947</v>
+        <v>26.6891</v>
       </c>
       <c r="G79" t="n">
-        <v>0</v>
+        <v>57.4727</v>
       </c>
     </row>
     <row r="80">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8811</v>
+        <v>0.8809</v>
       </c>
       <c r="F80" t="n">
-        <v>34.2628</v>
+        <v>34.2684</v>
       </c>
       <c r="G80" t="n">
-        <v>0</v>
+        <v>57.4455</v>
       </c>
     </row>
     <row r="81">
@@ -2760,17 +2760,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8502</v>
+        <v>0.8505</v>
       </c>
       <c r="F81" t="n">
-        <v>38.0246</v>
+        <v>38.0116</v>
       </c>
       <c r="G81" t="n">
-        <v>0</v>
+        <v>56.6721</v>
       </c>
     </row>
     <row r="82">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8476</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="F82" t="n">
-        <v>38.2392</v>
+        <v>38.2528</v>
       </c>
       <c r="G82" t="n">
-        <v>0</v>
+        <v>57.0092</v>
       </c>
     </row>
     <row r="83">
@@ -2818,17 +2818,17 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.9348</v>
+        <v>0.93</v>
       </c>
       <c r="F83" t="n">
-        <v>24.1615</v>
+        <v>24.7672</v>
       </c>
       <c r="G83" t="n">
-        <v>0</v>
+        <v>44.1722</v>
       </c>
     </row>
     <row r="84">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9341</v>
+        <v>0.9308</v>
       </c>
       <c r="F84" t="n">
-        <v>24.2616</v>
+        <v>24.6533</v>
       </c>
       <c r="G84" t="n">
-        <v>0</v>
+        <v>44.1975</v>
       </c>
     </row>
     <row r="85">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9352</v>
+        <v>0.9301</v>
       </c>
       <c r="F85" t="n">
-        <v>24.0806</v>
+        <v>24.7593</v>
       </c>
       <c r="G85" t="n">
-        <v>0</v>
+        <v>44.1949</v>
       </c>
     </row>
     <row r="86">
@@ -2905,17 +2905,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.9646</v>
+        <v>0.964</v>
       </c>
       <c r="F86" t="n">
-        <v>18.69</v>
+        <v>18.7919</v>
       </c>
       <c r="G86" t="n">
-        <v>0</v>
+        <v>41.2281</v>
       </c>
     </row>
     <row r="87">
@@ -2934,17 +2934,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.9502</v>
+        <v>0.95</v>
       </c>
       <c r="F87" t="n">
-        <v>21.3582</v>
+        <v>21.3739</v>
       </c>
       <c r="G87" t="n">
-        <v>0</v>
+        <v>41.4478</v>
       </c>
     </row>
     <row r="88">
@@ -2963,17 +2963,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.954</v>
+        <v>0.9537</v>
       </c>
       <c r="F88" t="n">
-        <v>21.0063</v>
+        <v>21.0797</v>
       </c>
       <c r="G88" t="n">
-        <v>0</v>
+        <v>41.9511</v>
       </c>
     </row>
     <row r="89">
@@ -2992,17 +2992,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9463</v>
+        <v>0.9351</v>
       </c>
       <c r="F89" t="n">
-        <v>22.8844</v>
+        <v>24.4372</v>
       </c>
       <c r="G89" t="n">
-        <v>0</v>
+        <v>41.8251</v>
       </c>
     </row>
     <row r="90">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9448</v>
+        <v>0.9447</v>
       </c>
       <c r="F90" t="n">
-        <v>23.2663</v>
+        <v>23.2666</v>
       </c>
       <c r="G90" t="n">
-        <v>0</v>
+        <v>40.6393</v>
       </c>
     </row>
     <row r="91">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9474</v>
+        <v>0.9475</v>
       </c>
       <c r="F91" t="n">
-        <v>22.4777</v>
+        <v>22.4672</v>
       </c>
       <c r="G91" t="n">
-        <v>0</v>
+        <v>39.9884</v>
       </c>
     </row>
     <row r="92">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.954</v>
+        <v>0.9537</v>
       </c>
       <c r="F92" t="n">
-        <v>21.0063</v>
+        <v>21.0797</v>
       </c>
       <c r="G92" t="n">
-        <v>0</v>
+        <v>41.9511</v>
       </c>
     </row>
     <row r="93">
@@ -3108,17 +3108,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9474</v>
+        <v>0.9475</v>
       </c>
       <c r="F93" t="n">
-        <v>22.4777</v>
+        <v>22.4672</v>
       </c>
       <c r="G93" t="n">
-        <v>0</v>
+        <v>39.9884</v>
       </c>
     </row>
     <row r="94">
@@ -3137,17 +3137,17 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9267</v>
+        <v>0.9265</v>
       </c>
       <c r="F94" t="n">
-        <v>25.6435</v>
+        <v>25.6773</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>43.7205</v>
       </c>
     </row>
     <row r="95">
@@ -3166,17 +3166,17 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.8991</v>
+        <v>0.7848000000000001</v>
       </c>
       <c r="F95" t="n">
-        <v>34.7001</v>
+        <v>47.1317</v>
       </c>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>68.43519999999999</v>
       </c>
     </row>
     <row r="96">
@@ -3195,17 +3195,17 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9272</v>
+        <v>0.9268999999999999</v>
       </c>
       <c r="F96" t="n">
-        <v>25.5219</v>
+        <v>25.5813</v>
       </c>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>43.5663</v>
       </c>
     </row>
     <row r="97">
@@ -3224,17 +3224,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9268</v>
+        <v>0.9265</v>
       </c>
       <c r="F97" t="n">
-        <v>25.5687</v>
+        <v>25.6296</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>43.6045</v>
       </c>
     </row>
     <row r="98">
@@ -3253,17 +3253,17 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9468</v>
+        <v>0.9474</v>
       </c>
       <c r="F98" t="n">
-        <v>22.6125</v>
+        <v>22.5343</v>
       </c>
       <c r="G98" t="n">
-        <v>0</v>
+        <v>40.2419</v>
       </c>
     </row>
     <row r="99">
@@ -3282,17 +3282,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.971</v>
+        <v>0.9635</v>
       </c>
       <c r="F99" t="n">
-        <v>17.3031</v>
+        <v>19.3477</v>
       </c>
       <c r="G99" t="n">
-        <v>0</v>
+        <v>40.3837</v>
       </c>
     </row>
     <row r="100">
@@ -3311,17 +3311,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9795</v>
+        <v>0.9312</v>
       </c>
       <c r="F100" t="n">
-        <v>15.1033</v>
+        <v>25.322</v>
       </c>
       <c r="G100" t="n">
-        <v>0</v>
+        <v>40.3612</v>
       </c>
     </row>
     <row r="101">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9616</v>
+        <v>0.9618</v>
       </c>
       <c r="F101" t="n">
-        <v>19.7246</v>
+        <v>19.6167</v>
       </c>
       <c r="G101" t="n">
-        <v>0</v>
+        <v>40.2966</v>
       </c>
     </row>
     <row r="102">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9391</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="F102" t="n">
-        <v>23.6111</v>
+        <v>23.631</v>
       </c>
       <c r="G102" t="n">
-        <v>0</v>
+        <v>40.4327</v>
       </c>
     </row>
     <row r="103">
@@ -3398,17 +3398,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9665</v>
+        <v>0.9757</v>
       </c>
       <c r="F103" t="n">
-        <v>18.4903</v>
+        <v>16.1569</v>
       </c>
       <c r="G103" t="n">
-        <v>0</v>
+        <v>39.8523</v>
       </c>
     </row>
     <row r="104">
@@ -3427,17 +3427,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E104" t="n">
         <v>0.9372</v>
       </c>
       <c r="F104" t="n">
-        <v>24.6202</v>
+        <v>24.6145</v>
       </c>
       <c r="G104" t="n">
-        <v>0</v>
+        <v>40.8747</v>
       </c>
     </row>
     <row r="105">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9316</v>
+        <v>0.9666</v>
       </c>
       <c r="F105" t="n">
-        <v>25.5653</v>
+        <v>18.7989</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>40.8068</v>
       </c>
     </row>
     <row r="106">
@@ -3485,17 +3485,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9345</v>
+        <v>0.9342</v>
       </c>
       <c r="F106" t="n">
-        <v>24.9518</v>
+        <v>25.0083</v>
       </c>
       <c r="G106" t="n">
-        <v>0</v>
+        <v>40.4422</v>
       </c>
     </row>
     <row r="107">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.9772</v>
       </c>
       <c r="F107" t="n">
-        <v>15.4278</v>
+        <v>15.4265</v>
       </c>
       <c r="G107" t="n">
-        <v>0</v>
+        <v>40.4295</v>
       </c>
     </row>
     <row r="108">
@@ -3543,17 +3543,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.9349</v>
       </c>
       <c r="F108" t="n">
-        <v>25.4384</v>
+        <v>25.4454</v>
       </c>
       <c r="G108" t="n">
-        <v>0</v>
+        <v>44.1909</v>
       </c>
     </row>
     <row r="109">
@@ -3572,17 +3572,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9383</v>
+        <v>0.9381</v>
       </c>
       <c r="F109" t="n">
-        <v>24.7347</v>
+        <v>24.7831</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>43.8199</v>
       </c>
     </row>
     <row r="110">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9815</v>
+        <v>0.9811</v>
       </c>
       <c r="F110" t="n">
-        <v>14.9006</v>
+        <v>15.1634</v>
       </c>
       <c r="G110" t="n">
-        <v>0</v>
+        <v>43.6275</v>
       </c>
     </row>
     <row r="111">
@@ -3630,17 +3630,17 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9825</v>
+        <v>0.9821</v>
       </c>
       <c r="F111" t="n">
-        <v>14.3087</v>
+        <v>14.5135</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>42.3931</v>
       </c>
     </row>
     <row r="112">
@@ -3659,17 +3659,17 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
         <v>0.9362</v>
       </c>
       <c r="F112" t="n">
-        <v>25.2357</v>
+        <v>25.222</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>44.1881</v>
       </c>
     </row>
     <row r="113">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9387</v>
+        <v>0.9385</v>
       </c>
       <c r="F113" t="n">
-        <v>24.7233</v>
+        <v>24.7706</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>43.8706</v>
       </c>
     </row>
     <row r="114">
@@ -3717,17 +3717,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9666</v>
+        <v>0.9811</v>
       </c>
       <c r="F114" t="n">
-        <v>18.9522</v>
+        <v>15.1581</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>43.6001</v>
       </c>
     </row>
     <row r="115">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9822</v>
+        <v>0.9817</v>
       </c>
       <c r="F115" t="n">
-        <v>14.4552</v>
+        <v>14.6775</v>
       </c>
       <c r="G115" t="n">
-        <v>0</v>
+        <v>42.5479</v>
       </c>
     </row>
     <row r="116">
@@ -3775,17 +3775,17 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.8247</v>
+        <v>0.8248</v>
       </c>
       <c r="F116" t="n">
-        <v>40.6038</v>
+        <v>40.6032</v>
       </c>
       <c r="G116" t="n">
-        <v>0</v>
+        <v>58.5079</v>
       </c>
     </row>
     <row r="117">
@@ -3804,17 +3804,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8238</v>
+        <v>0.8242</v>
       </c>
       <c r="F117" t="n">
-        <v>40.6861</v>
+        <v>40.6691</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>58.3656</v>
       </c>
     </row>
     <row r="118">
@@ -3833,17 +3833,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9316</v>
+        <v>0.9666</v>
       </c>
       <c r="F118" t="n">
-        <v>25.5653</v>
+        <v>18.7989</v>
       </c>
       <c r="G118" t="n">
-        <v>0</v>
+        <v>40.8068</v>
       </c>
     </row>
     <row r="119">
@@ -3862,17 +3862,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9387</v>
+        <v>0.9385</v>
       </c>
       <c r="F119" t="n">
-        <v>24.7233</v>
+        <v>24.7705</v>
       </c>
       <c r="G119" t="n">
-        <v>0</v>
+        <v>43.8706</v>
       </c>
     </row>
     <row r="120">
@@ -3891,17 +3891,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9332</v>
       </c>
       <c r="F120" t="n">
-        <v>22.1297</v>
+        <v>24.5573</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>46.4371</v>
       </c>
     </row>
     <row r="121">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9471000000000001</v>
+        <v>0.9332</v>
       </c>
       <c r="F121" t="n">
-        <v>22.1297</v>
+        <v>24.5573</v>
       </c>
       <c r="G121" t="n">
-        <v>0</v>
+        <v>46.4371</v>
       </c>
     </row>
     <row r="122">
@@ -3949,17 +3949,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E122" t="n">
         <v>0.9327</v>
       </c>
       <c r="F122" t="n">
-        <v>24.2728</v>
+        <v>24.2758</v>
       </c>
       <c r="G122" t="n">
-        <v>0</v>
+        <v>41.4573</v>
       </c>
     </row>
     <row r="123">
@@ -3978,17 +3978,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9386</v>
+        <v>0.9384</v>
       </c>
       <c r="F123" t="n">
-        <v>24.7427</v>
+        <v>24.7904</v>
       </c>
       <c r="G123" t="n">
-        <v>0</v>
+        <v>43.8808</v>
       </c>
     </row>
     <row r="124">
@@ -4007,17 +4007,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9677</v>
+        <v>0.9804</v>
       </c>
       <c r="F124" t="n">
-        <v>18.7631</v>
+        <v>16.0758</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>43.7372</v>
       </c>
     </row>
     <row r="125">
@@ -4036,17 +4036,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9765</v>
+        <v>0.9766</v>
       </c>
       <c r="F125" t="n">
-        <v>15.6467</v>
+        <v>15.6321</v>
       </c>
       <c r="G125" t="n">
-        <v>0</v>
+        <v>43.6614</v>
       </c>
     </row>
     <row r="126">
@@ -4065,17 +4065,17 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E126" t="n">
         <v>0.9374</v>
       </c>
       <c r="F126" t="n">
-        <v>23.8183</v>
+        <v>23.8029</v>
       </c>
       <c r="G126" t="n">
-        <v>0</v>
+        <v>41.9383</v>
       </c>
     </row>
     <row r="127">
@@ -4094,17 +4094,17 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8124</v>
+        <v>0.8128</v>
       </c>
       <c r="F127" t="n">
-        <v>41.2452</v>
+        <v>41.2129</v>
       </c>
       <c r="G127" t="n">
-        <v>0</v>
+        <v>59.9333</v>
       </c>
     </row>
     <row r="128">
@@ -4123,17 +4123,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9364</v>
+        <v>0.9598</v>
       </c>
       <c r="F128" t="n">
-        <v>23.9207</v>
+        <v>19.6326</v>
       </c>
       <c r="G128" t="n">
-        <v>0</v>
+        <v>41.7819</v>
       </c>
     </row>
     <row r="129">
@@ -4152,17 +4152,17 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.9679</v>
+        <v>0.968</v>
       </c>
       <c r="F129" t="n">
-        <v>17.4643</v>
+        <v>17.451</v>
       </c>
       <c r="G129" t="n">
-        <v>0</v>
+        <v>41.8212</v>
       </c>
     </row>
     <row r="130">
@@ -4181,17 +4181,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9612000000000001</v>
+        <v>0.9613</v>
       </c>
       <c r="F130" t="n">
-        <v>19.3751</v>
+        <v>19.4069</v>
       </c>
       <c r="G130" t="n">
-        <v>0</v>
+        <v>41.8309</v>
       </c>
     </row>
     <row r="131">
@@ -4210,17 +4210,17 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9681</v>
+        <v>0.9613</v>
       </c>
       <c r="F131" t="n">
-        <v>17.3954</v>
+        <v>19.4316</v>
       </c>
       <c r="G131" t="n">
-        <v>0</v>
+        <v>41.6089</v>
       </c>
     </row>
     <row r="132">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9608</v>
+        <v>0.9684</v>
       </c>
       <c r="F132" t="n">
-        <v>19.3631</v>
+        <v>17.3323</v>
       </c>
       <c r="G132" t="n">
-        <v>0</v>
+        <v>41.6724</v>
       </c>
     </row>
     <row r="133">
@@ -4268,17 +4268,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9683</v>
+        <v>0.9686</v>
       </c>
       <c r="F133" t="n">
-        <v>17.3444</v>
+        <v>17.3021</v>
       </c>
       <c r="G133" t="n">
-        <v>0</v>
+        <v>41.7896</v>
       </c>
     </row>
     <row r="134">
@@ -4297,17 +4297,17 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9374</v>
+        <v>0.9797</v>
       </c>
       <c r="F134" t="n">
-        <v>23.7491</v>
+        <v>14.6209</v>
       </c>
       <c r="G134" t="n">
-        <v>0</v>
+        <v>41.7437</v>
       </c>
     </row>
     <row r="135">
@@ -4326,17 +4326,17 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.9597</v>
+        <v>0.96</v>
       </c>
       <c r="F135" t="n">
-        <v>19.631</v>
+        <v>19.5844</v>
       </c>
       <c r="G135" t="n">
-        <v>0</v>
+        <v>41.7565</v>
       </c>
     </row>
     <row r="136">
@@ -4355,17 +4355,17 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E136" t="n">
         <v>0.968</v>
       </c>
       <c r="F136" t="n">
-        <v>17.3999</v>
+        <v>17.4409</v>
       </c>
       <c r="G136" t="n">
-        <v>0</v>
+        <v>41.6549</v>
       </c>
     </row>
     <row r="137">
@@ -4384,17 +4384,17 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9765</v>
+        <v>0.9757</v>
       </c>
       <c r="F137" t="n">
-        <v>15.1604</v>
+        <v>15.276</v>
       </c>
       <c r="G137" t="n">
-        <v>0</v>
+        <v>39.2445</v>
       </c>
     </row>
     <row r="138">
@@ -4413,17 +4413,17 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9765</v>
+        <v>0.9761</v>
       </c>
       <c r="F138" t="n">
-        <v>15.6088</v>
+        <v>15.6221</v>
       </c>
       <c r="G138" t="n">
-        <v>0</v>
+        <v>39.5832</v>
       </c>
     </row>
     <row r="139">
@@ -4442,17 +4442,17 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9281</v>
+        <v>0.9278999999999999</v>
       </c>
       <c r="F139" t="n">
-        <v>24.8813</v>
+        <v>24.931</v>
       </c>
       <c r="G139" t="n">
-        <v>0</v>
+        <v>39.6549</v>
       </c>
     </row>
     <row r="140">
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.955</v>
+        <v>0.9472</v>
       </c>
       <c r="F140" t="n">
-        <v>20.6591</v>
+        <v>22.3945</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>39.3913</v>
       </c>
     </row>
     <row r="141">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9297</v>
+        <v>0.9298</v>
       </c>
       <c r="F141" t="n">
-        <v>25.8217</v>
+        <v>25.806</v>
       </c>
       <c r="G141" t="n">
-        <v>0</v>
+        <v>39.8611</v>
       </c>
     </row>
     <row r="142">
@@ -4529,17 +4529,17 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9765</v>
+        <v>0.9761</v>
       </c>
       <c r="F142" t="n">
-        <v>15.6088</v>
+        <v>15.6221</v>
       </c>
       <c r="G142" t="n">
-        <v>0</v>
+        <v>39.5832</v>
       </c>
     </row>
     <row r="143">
@@ -4558,17 +4558,17 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9308</v>
+        <v>0.9313</v>
       </c>
       <c r="F143" t="n">
-        <v>24.4782</v>
+        <v>24.4046</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>39.6758</v>
       </c>
     </row>
     <row r="144">
@@ -4587,17 +4587,17 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9311</v>
+        <v>0.9313</v>
       </c>
       <c r="F144" t="n">
-        <v>24.4768</v>
+        <v>24.4502</v>
       </c>
       <c r="G144" t="n">
-        <v>0</v>
+        <v>39.7665</v>
       </c>
     </row>
     <row r="145">
@@ -4616,17 +4616,17 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9297</v>
+        <v>0.9298</v>
       </c>
       <c r="F145" t="n">
-        <v>25.8217</v>
+        <v>25.806</v>
       </c>
       <c r="G145" t="n">
-        <v>0</v>
+        <v>39.8611</v>
       </c>
     </row>
     <row r="146">
@@ -4645,17 +4645,17 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.8114</v>
+        <v>0.8117</v>
       </c>
       <c r="F146" t="n">
-        <v>41.2864</v>
+        <v>41.2649</v>
       </c>
       <c r="G146" t="n">
-        <v>0</v>
+        <v>59.8362</v>
       </c>
     </row>
     <row r="147">
@@ -4674,17 +4674,17 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E147" t="n">
         <v>0.8117</v>
       </c>
       <c r="F147" t="n">
-        <v>41.2321</v>
+        <v>41.2352</v>
       </c>
       <c r="G147" t="n">
-        <v>0</v>
+        <v>59.8089</v>
       </c>
     </row>
     <row r="148">
@@ -4703,17 +4703,17 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.8113</v>
+        <v>0.8117</v>
       </c>
       <c r="F148" t="n">
-        <v>41.1853</v>
+        <v>41.1723</v>
       </c>
       <c r="G148" t="n">
-        <v>0</v>
+        <v>59.8646</v>
       </c>
     </row>
     <row r="149">
@@ -4732,17 +4732,17 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.8127</v>
+        <v>0.8129</v>
       </c>
       <c r="F149" t="n">
-        <v>41.0663</v>
+        <v>41.0549</v>
       </c>
       <c r="G149" t="n">
-        <v>0</v>
+        <v>59.8899</v>
       </c>
     </row>
     <row r="150">
@@ -4761,17 +4761,17 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.8126</v>
+        <v>0.8131</v>
       </c>
       <c r="F150" t="n">
-        <v>41.2126</v>
+        <v>41.1718</v>
       </c>
       <c r="G150" t="n">
-        <v>0</v>
+        <v>59.9506</v>
       </c>
     </row>
     <row r="151">
@@ -4790,17 +4790,17 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8125</v>
+        <v>0.8131</v>
       </c>
       <c r="F151" t="n">
-        <v>41.2163</v>
+        <v>41.1741</v>
       </c>
       <c r="G151" t="n">
-        <v>0</v>
+        <v>59.9109</v>
       </c>
     </row>
     <row r="152">
@@ -4819,17 +4819,17 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.8143</v>
+        <v>0.8147</v>
       </c>
       <c r="F152" t="n">
-        <v>41.1196</v>
+        <v>41.086</v>
       </c>
       <c r="G152" t="n">
-        <v>0</v>
+        <v>59.9441</v>
       </c>
     </row>
     <row r="153">
@@ -4848,17 +4848,17 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.8136</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="F153" t="n">
-        <v>41.133</v>
+        <v>41.1103</v>
       </c>
       <c r="G153" t="n">
-        <v>0</v>
+        <v>59.9469</v>
       </c>
     </row>
     <row r="154">
@@ -4877,17 +4877,17 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8104</v>
+        <v>0.8106</v>
       </c>
       <c r="F154" t="n">
-        <v>41.3276</v>
+        <v>41.3209</v>
       </c>
       <c r="G154" t="n">
-        <v>0</v>
+        <v>60.0346</v>
       </c>
     </row>
     <row r="155">
@@ -4906,17 +4906,17 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8313</v>
+        <v>0.8310999999999999</v>
       </c>
       <c r="F155" t="n">
-        <v>39.6102</v>
+        <v>39.6303</v>
       </c>
       <c r="G155" t="n">
-        <v>0</v>
+        <v>58.6658</v>
       </c>
     </row>
     <row r="156">
@@ -4935,17 +4935,17 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.833</v>
+        <v>0.8331</v>
       </c>
       <c r="F156" t="n">
-        <v>39.4924</v>
+        <v>39.4958</v>
       </c>
       <c r="G156" t="n">
-        <v>0</v>
+        <v>58.8995</v>
       </c>
     </row>
     <row r="157">
@@ -4964,17 +4964,17 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.8335</v>
+        <v>0.8336</v>
       </c>
       <c r="F157" t="n">
-        <v>39.3777</v>
+        <v>39.3823</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>59.0369</v>
       </c>
     </row>
     <row r="158">
@@ -4993,17 +4993,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.8368</v>
+        <v>0.8366</v>
       </c>
       <c r="F158" t="n">
-        <v>39.4621</v>
+        <v>39.4645</v>
       </c>
       <c r="G158" t="n">
-        <v>0</v>
+        <v>56.9446</v>
       </c>
     </row>
     <row r="159">
@@ -5022,17 +5022,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9769</v>
+        <v>0.9736</v>
       </c>
       <c r="F159" t="n">
-        <v>15.1165</v>
+        <v>16.0301</v>
       </c>
       <c r="G159" t="n">
-        <v>0</v>
+        <v>42.5221</v>
       </c>
     </row>
     <row r="160">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8161</v>
+        <v>0.8164</v>
       </c>
       <c r="F160" t="n">
-        <v>40.7764</v>
+        <v>40.775</v>
       </c>
       <c r="G160" t="n">
-        <v>0</v>
+        <v>58.9446</v>
       </c>
     </row>
     <row r="161">
@@ -5080,17 +5080,17 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8144</v>
+        <v>0.8146</v>
       </c>
       <c r="F161" t="n">
-        <v>40.871</v>
+        <v>40.8601</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>58.9743</v>
       </c>
     </row>
     <row r="162">
@@ -5109,17 +5109,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9736</v>
+        <v>0.9752</v>
       </c>
       <c r="F162" t="n">
-        <v>15.8313</v>
+        <v>15.5208</v>
       </c>
       <c r="G162" t="n">
-        <v>0</v>
+        <v>42.8121</v>
       </c>
     </row>
     <row r="163">
@@ -5138,17 +5138,17 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9381</v>
+        <v>0.9386</v>
       </c>
       <c r="F163" t="n">
-        <v>23.32</v>
+        <v>23.2084</v>
       </c>
       <c r="G163" t="n">
-        <v>0</v>
+        <v>40.0892</v>
       </c>
     </row>
     <row r="164">
@@ -5167,17 +5167,17 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.9548</v>
+        <v>0.98</v>
       </c>
       <c r="F164" t="n">
-        <v>20.6967</v>
+        <v>14.6251</v>
       </c>
       <c r="G164" t="n">
-        <v>0</v>
+        <v>39.3099</v>
       </c>
     </row>
     <row r="165">
@@ -5196,17 +5196,17 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9765</v>
+        <v>0.9766</v>
       </c>
       <c r="F165" t="n">
-        <v>15.6467</v>
+        <v>15.6321</v>
       </c>
       <c r="G165" t="n">
-        <v>0</v>
+        <v>43.6614</v>
       </c>
     </row>
     <row r="166">
@@ -5225,17 +5225,17 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.8985</v>
+        <v>0.8994</v>
       </c>
       <c r="F166" t="n">
-        <v>34.734</v>
+        <v>34.6214</v>
       </c>
       <c r="G166" t="n">
-        <v>0</v>
+        <v>68.3343</v>
       </c>
     </row>
     <row r="167">
@@ -5254,17 +5254,17 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E167" t="n">
         <v>0.9317</v>
       </c>
       <c r="F167" t="n">
-        <v>24.5085</v>
+        <v>24.5121</v>
       </c>
       <c r="G167" t="n">
-        <v>0</v>
+        <v>39.6886</v>
       </c>
     </row>
     <row r="168">
@@ -5283,17 +5283,17 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9391</v>
       </c>
       <c r="F168" t="n">
-        <v>24.4076</v>
+        <v>24.3951</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>39.5112</v>
       </c>
     </row>
     <row r="169">
@@ -5312,17 +5312,17 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9506</v>
+        <v>0.9504</v>
       </c>
       <c r="F169" t="n">
-        <v>21.216</v>
+        <v>21.2894</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>41.4185</v>
       </c>
     </row>
     <row r="170">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9558</v>
+        <v>0.9556</v>
       </c>
       <c r="F170" t="n">
-        <v>20.9642</v>
+        <v>20.9823</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>43.2193</v>
       </c>
     </row>
     <row r="171">
@@ -5370,17 +5370,17 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E171" t="n">
         <v>0.9444</v>
       </c>
       <c r="F171" t="n">
-        <v>23.2271</v>
+        <v>23.233</v>
       </c>
       <c r="G171" t="n">
-        <v>0</v>
+        <v>40.6209</v>
       </c>
     </row>
     <row r="172">
@@ -5399,17 +5399,17 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Erreur extraction</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9385</v>
       </c>
       <c r="F172" t="n">
-        <v>23.1955</v>
+        <v>23.5341</v>
       </c>
       <c r="G172" t="n">
-        <v>0</v>
+        <v>39.738</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X9.cis.beta.carotene/RANDOMSEARCH_DETAILS_X9.cis.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X9.cis.beta.carotene/RANDOMSEARCH_DETAILS_X9.cis.beta.carotene.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G172"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,10 +444,15 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>R2cv</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>RMSEC</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>RMSECV</t>
         </is>
@@ -476,9 +481,12 @@
         <v>0.9559</v>
       </c>
       <c r="F2" t="n">
+        <v>1.3991</v>
+      </c>
+      <c r="G2" t="n">
         <v>20.1046</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>41.4024</v>
       </c>
     </row>
@@ -505,9 +513,12 @@
         <v>0.9699</v>
       </c>
       <c r="F3" t="n">
+        <v>1.3937</v>
+      </c>
+      <c r="G3" t="n">
         <v>17.1809</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>41.1195</v>
       </c>
     </row>
@@ -534,9 +545,12 @@
         <v>0.9265</v>
       </c>
       <c r="F4" t="n">
+        <v>1.4451</v>
+      </c>
+      <c r="G4" t="n">
         <v>25.6773</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>43.7205</v>
       </c>
     </row>
@@ -563,9 +577,12 @@
         <v>0.8629</v>
       </c>
       <c r="F5" t="n">
+        <v>1.7908</v>
+      </c>
+      <c r="G5" t="n">
         <v>36.8947</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>58.2762</v>
       </c>
     </row>
@@ -592,9 +609,12 @@
         <v>0.9414</v>
       </c>
       <c r="F6" t="n">
+        <v>1.7804</v>
+      </c>
+      <c r="G6" t="n">
         <v>26.7918</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>57.8911</v>
       </c>
     </row>
@@ -621,9 +641,12 @@
         <v>0.9315</v>
       </c>
       <c r="F7" t="n">
+        <v>1.4352</v>
+      </c>
+      <c r="G7" t="n">
         <v>24.3001</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>43.2339</v>
       </c>
     </row>
@@ -650,9 +673,12 @@
         <v>0.9633</v>
       </c>
       <c r="F8" t="n">
+        <v>1.4662</v>
+      </c>
+      <c r="G8" t="n">
         <v>18.9322</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>44.7461</v>
       </c>
     </row>
@@ -672,16 +698,19 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E9" t="n">
         <v>0.9447</v>
       </c>
       <c r="F9" t="n">
+        <v>1.3988</v>
+      </c>
+      <c r="G9" t="n">
         <v>23.1559</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>41.3857</v>
       </c>
     </row>
@@ -708,9 +737,12 @@
         <v>0.9626</v>
       </c>
       <c r="F10" t="n">
+        <v>1.4678</v>
+      </c>
+      <c r="G10" t="n">
         <v>19.0434</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>44.8206</v>
       </c>
     </row>
@@ -737,9 +769,12 @@
         <v>0.9576</v>
       </c>
       <c r="F11" t="n">
+        <v>1.4649</v>
+      </c>
+      <c r="G11" t="n">
         <v>19.9166</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>44.6816</v>
       </c>
     </row>
@@ -766,9 +801,12 @@
         <v>0.9573</v>
       </c>
       <c r="F12" t="n">
+        <v>1.4619</v>
+      </c>
+      <c r="G12" t="n">
         <v>19.9448</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>44.5388</v>
       </c>
     </row>
@@ -795,9 +833,12 @@
         <v>0.9631</v>
       </c>
       <c r="F13" t="n">
+        <v>1.4472</v>
+      </c>
+      <c r="G13" t="n">
         <v>18.8356</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>43.8248</v>
       </c>
     </row>
@@ -824,9 +865,12 @@
         <v>0.9391</v>
       </c>
       <c r="F14" t="n">
+        <v>1.4682</v>
+      </c>
+      <c r="G14" t="n">
         <v>23.4291</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>44.842</v>
       </c>
     </row>
@@ -853,9 +897,12 @@
         <v>0.9573</v>
       </c>
       <c r="F15" t="n">
+        <v>1.4619</v>
+      </c>
+      <c r="G15" t="n">
         <v>19.9497</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>44.5383</v>
       </c>
     </row>
@@ -882,9 +929,12 @@
         <v>0.9564</v>
       </c>
       <c r="F16" t="n">
+        <v>1.4572</v>
+      </c>
+      <c r="G16" t="n">
         <v>20.1341</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>44.3105</v>
       </c>
     </row>
@@ -911,9 +961,12 @@
         <v>0.9629</v>
       </c>
       <c r="F17" t="n">
+        <v>1.4474</v>
+      </c>
+      <c r="G17" t="n">
         <v>18.9246</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>43.8365</v>
       </c>
     </row>
@@ -940,9 +993,12 @@
         <v>0.9352</v>
       </c>
       <c r="F18" t="n">
+        <v>1.3984</v>
+      </c>
+      <c r="G18" t="n">
         <v>24.3446</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>41.3663</v>
       </c>
     </row>
@@ -969,9 +1025,12 @@
         <v>0.9340000000000001</v>
       </c>
       <c r="F19" t="n">
+        <v>1.403</v>
+      </c>
+      <c r="G19" t="n">
         <v>24.5113</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>41.6025</v>
       </c>
     </row>
@@ -998,9 +1057,12 @@
         <v>0.9215</v>
       </c>
       <c r="F20" t="n">
+        <v>1.4075</v>
+      </c>
+      <c r="G20" t="n">
         <v>26.665</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>41.8334</v>
       </c>
     </row>
@@ -1027,9 +1089,12 @@
         <v>0.9206</v>
       </c>
       <c r="F21" t="n">
+        <v>1.4056</v>
+      </c>
+      <c r="G21" t="n">
         <v>26.7647</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>41.7354</v>
       </c>
     </row>
@@ -1056,9 +1121,12 @@
         <v>0.9565</v>
       </c>
       <c r="F22" t="n">
+        <v>1.4034</v>
+      </c>
+      <c r="G22" t="n">
         <v>20.5006</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>41.6238</v>
       </c>
     </row>
@@ -1078,16 +1146,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>0.9365</v>
       </c>
       <c r="F23" t="n">
+        <v>1.4085</v>
+      </c>
+      <c r="G23" t="n">
         <v>23.5494</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>41.8873</v>
       </c>
     </row>
@@ -1114,9 +1185,12 @@
         <v>0.9302</v>
       </c>
       <c r="F24" t="n">
+        <v>1.4088</v>
+      </c>
+      <c r="G24" t="n">
         <v>25.0567</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>41.8984</v>
       </c>
     </row>
@@ -1143,9 +1217,12 @@
         <v>0.9192</v>
       </c>
       <c r="F25" t="n">
+        <v>1.4149</v>
+      </c>
+      <c r="G25" t="n">
         <v>26.9596</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>42.2101</v>
       </c>
     </row>
@@ -1165,16 +1242,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E26" t="n">
         <v>0.95</v>
       </c>
       <c r="F26" t="n">
+        <v>1.4014</v>
+      </c>
+      <c r="G26" t="n">
         <v>21.374</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>41.5208</v>
       </c>
     </row>
@@ -1201,9 +1281,12 @@
         <v>0.9294</v>
       </c>
       <c r="F27" t="n">
+        <v>1.4063</v>
+      </c>
+      <c r="G27" t="n">
         <v>25.5904</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>41.7723</v>
       </c>
     </row>
@@ -1230,9 +1313,12 @@
         <v>0.9464</v>
       </c>
       <c r="F28" t="n">
+        <v>1.4052</v>
+      </c>
+      <c r="G28" t="n">
         <v>21.8518</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>41.7148</v>
       </c>
     </row>
@@ -1259,9 +1345,12 @@
         <v>0.9338</v>
       </c>
       <c r="F29" t="n">
+        <v>1.4086</v>
+      </c>
+      <c r="G29" t="n">
         <v>24.4841</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>41.8887</v>
       </c>
     </row>
@@ -1288,9 +1377,12 @@
         <v>0.9584</v>
       </c>
       <c r="F30" t="n">
+        <v>1.4092</v>
+      </c>
+      <c r="G30" t="n">
         <v>20.3849</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>41.921</v>
       </c>
     </row>
@@ -1317,9 +1409,12 @@
         <v>0.9206</v>
       </c>
       <c r="F31" t="n">
+        <v>1.403</v>
+      </c>
+      <c r="G31" t="n">
         <v>26.8066</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>41.604</v>
       </c>
     </row>
@@ -1346,9 +1441,12 @@
         <v>0.9137999999999999</v>
       </c>
       <c r="F32" t="n">
+        <v>1.4094</v>
+      </c>
+      <c r="G32" t="n">
         <v>27.8922</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>41.933</v>
       </c>
     </row>
@@ -1375,9 +1473,12 @@
         <v>0.9577</v>
       </c>
       <c r="F33" t="n">
+        <v>1.4056</v>
+      </c>
+      <c r="G33" t="n">
         <v>20.3422</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>41.736</v>
       </c>
     </row>
@@ -1404,9 +1505,12 @@
         <v>0.9723000000000001</v>
       </c>
       <c r="F34" t="n">
+        <v>1.3784</v>
+      </c>
+      <c r="G34" t="n">
         <v>16.5521</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>40.3146</v>
       </c>
     </row>
@@ -1433,9 +1537,12 @@
         <v>0.9467</v>
       </c>
       <c r="F35" t="n">
+        <v>1.3847</v>
+      </c>
+      <c r="G35" t="n">
         <v>22.8522</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>40.6447</v>
       </c>
     </row>
@@ -1455,16 +1562,19 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>0.9455</v>
       </c>
       <c r="F36" t="n">
+        <v>1.3807</v>
+      </c>
+      <c r="G36" t="n">
         <v>23.0929</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>40.4369</v>
       </c>
     </row>
@@ -1491,9 +1601,12 @@
         <v>0.9473</v>
       </c>
       <c r="F37" t="n">
+        <v>1.3715</v>
+      </c>
+      <c r="G37" t="n">
         <v>22.4584</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>39.9443</v>
       </c>
     </row>
@@ -1520,9 +1633,12 @@
         <v>0.9435</v>
       </c>
       <c r="F38" t="n">
+        <v>1.3746</v>
+      </c>
+      <c r="G38" t="n">
         <v>23.0092</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>40.1105</v>
       </c>
     </row>
@@ -1549,9 +1665,12 @@
         <v>0.9432</v>
       </c>
       <c r="F39" t="n">
+        <v>1.3769</v>
+      </c>
+      <c r="G39" t="n">
         <v>22.7951</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>40.2315</v>
       </c>
     </row>
@@ -1578,9 +1697,12 @@
         <v>0.945</v>
       </c>
       <c r="F40" t="n">
+        <v>1.3783</v>
+      </c>
+      <c r="G40" t="n">
         <v>22.6186</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>40.309</v>
       </c>
     </row>
@@ -1607,9 +1729,12 @@
         <v>0.9726</v>
       </c>
       <c r="F41" t="n">
+        <v>1.3799</v>
+      </c>
+      <c r="G41" t="n">
         <v>16.4738</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>40.3897</v>
       </c>
     </row>
@@ -1629,16 +1754,19 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
         <v>0.9466</v>
       </c>
       <c r="F42" t="n">
-        <v>22.8697</v>
+        <v>1.3879</v>
       </c>
       <c r="G42" t="n">
+        <v>22.8696</v>
+      </c>
+      <c r="H42" t="n">
         <v>40.8133</v>
       </c>
     </row>
@@ -1665,9 +1793,12 @@
         <v>0.9447</v>
       </c>
       <c r="F43" t="n">
+        <v>1.3849</v>
+      </c>
+      <c r="G43" t="n">
         <v>23.2662</v>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>40.6573</v>
       </c>
     </row>
@@ -1694,9 +1825,12 @@
         <v>0.9475</v>
       </c>
       <c r="F44" t="n">
+        <v>1.3724</v>
+      </c>
+      <c r="G44" t="n">
         <v>22.4681</v>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>39.9893</v>
       </c>
     </row>
@@ -1723,9 +1857,12 @@
         <v>0.9446</v>
       </c>
       <c r="F45" t="n">
+        <v>1.3627</v>
+      </c>
+      <c r="G45" t="n">
         <v>22.9149</v>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>39.4668</v>
       </c>
     </row>
@@ -1752,9 +1889,12 @@
         <v>0.9444</v>
       </c>
       <c r="F46" t="n">
+        <v>1.3791</v>
+      </c>
+      <c r="G46" t="n">
         <v>22.6427</v>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>40.3507</v>
       </c>
     </row>
@@ -1781,9 +1921,12 @@
         <v>0.9449</v>
       </c>
       <c r="F47" t="n">
+        <v>1.3852</v>
+      </c>
+      <c r="G47" t="n">
         <v>22.6568</v>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>40.673</v>
       </c>
     </row>
@@ -1803,16 +1946,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>0.9432</v>
       </c>
       <c r="F48" t="n">
+        <v>1.3936</v>
+      </c>
+      <c r="G48" t="n">
         <v>23.0784</v>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>41.115</v>
       </c>
     </row>
@@ -1839,9 +1985,12 @@
         <v>0.953</v>
       </c>
       <c r="F49" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G49" t="n">
         <v>20.8611</v>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>40.3967</v>
       </c>
     </row>
@@ -1868,9 +2017,12 @@
         <v>0.8914</v>
       </c>
       <c r="F50" t="n">
+        <v>1.775</v>
+      </c>
+      <c r="G50" t="n">
         <v>34.8317</v>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>57.6922</v>
       </c>
     </row>
@@ -1897,9 +2049,12 @@
         <v>0.8639</v>
       </c>
       <c r="F51" t="n">
+        <v>1.7649</v>
+      </c>
+      <c r="G51" t="n">
         <v>37.6518</v>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>57.3137</v>
       </c>
     </row>
@@ -1926,9 +2081,12 @@
         <v>0.8369</v>
       </c>
       <c r="F52" t="n">
+        <v>1.7591</v>
+      </c>
+      <c r="G52" t="n">
         <v>39.7738</v>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>57.0967</v>
       </c>
     </row>
@@ -1955,9 +2113,12 @@
         <v>0.8673999999999999</v>
       </c>
       <c r="F53" t="n">
+        <v>1.7486</v>
+      </c>
+      <c r="G53" t="n">
         <v>37.5511</v>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>56.7012</v>
       </c>
     </row>
@@ -1984,9 +2145,12 @@
         <v>0.8713</v>
       </c>
       <c r="F54" t="n">
+        <v>1.7255</v>
+      </c>
+      <c r="G54" t="n">
         <v>36.5813</v>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>55.8172</v>
       </c>
     </row>
@@ -2013,9 +2177,12 @@
         <v>0.8538</v>
       </c>
       <c r="F55" t="n">
+        <v>1.7721</v>
+      </c>
+      <c r="G55" t="n">
         <v>37.992</v>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>57.5836</v>
       </c>
     </row>
@@ -2042,9 +2209,12 @@
         <v>0.8615</v>
       </c>
       <c r="F56" t="n">
+        <v>1.7577</v>
+      </c>
+      <c r="G56" t="n">
         <v>37.9013</v>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>57.0436</v>
       </c>
     </row>
@@ -2071,9 +2241,12 @@
         <v>0.864</v>
       </c>
       <c r="F57" t="n">
+        <v>1.7466</v>
+      </c>
+      <c r="G57" t="n">
         <v>37.631</v>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>56.6254</v>
       </c>
     </row>
@@ -2100,9 +2273,12 @@
         <v>0.9408</v>
       </c>
       <c r="F58" t="n">
+        <v>1.7802</v>
+      </c>
+      <c r="G58" t="n">
         <v>26.9446</v>
       </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
         <v>57.8834</v>
       </c>
     </row>
@@ -2129,9 +2305,12 @@
         <v>0.9358</v>
       </c>
       <c r="F59" t="n">
+        <v>1.7798</v>
+      </c>
+      <c r="G59" t="n">
         <v>27.1568</v>
       </c>
-      <c r="G59" t="n">
+      <c r="H59" t="n">
         <v>57.8704</v>
       </c>
     </row>
@@ -2158,9 +2337,12 @@
         <v>0.9365</v>
       </c>
       <c r="F60" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="G60" t="n">
         <v>27.0186</v>
       </c>
-      <c r="G60" t="n">
+      <c r="H60" t="n">
         <v>57.876</v>
       </c>
     </row>
@@ -2187,9 +2369,12 @@
         <v>0.9396</v>
       </c>
       <c r="F61" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="G61" t="n">
         <v>27.0022</v>
       </c>
-      <c r="G61" t="n">
+      <c r="H61" t="n">
         <v>57.8034</v>
       </c>
     </row>
@@ -2216,9 +2401,12 @@
         <v>0.8415</v>
       </c>
       <c r="F62" t="n">
+        <v>1.7884</v>
+      </c>
+      <c r="G62" t="n">
         <v>38.5502</v>
       </c>
-      <c r="G62" t="n">
+      <c r="H62" t="n">
         <v>58.1883</v>
       </c>
     </row>
@@ -2245,9 +2433,12 @@
         <v>0.8608</v>
       </c>
       <c r="F63" t="n">
+        <v>1.7881</v>
+      </c>
+      <c r="G63" t="n">
         <v>36.5895</v>
       </c>
-      <c r="G63" t="n">
+      <c r="H63" t="n">
         <v>58.1783</v>
       </c>
     </row>
@@ -2274,9 +2465,12 @@
         <v>0.8692</v>
       </c>
       <c r="F64" t="n">
+        <v>1.7872</v>
+      </c>
+      <c r="G64" t="n">
         <v>36.1385</v>
       </c>
-      <c r="G64" t="n">
+      <c r="H64" t="n">
         <v>58.1433</v>
       </c>
     </row>
@@ -2303,9 +2497,12 @@
         <v>0.8613</v>
       </c>
       <c r="F65" t="n">
+        <v>1.7847</v>
+      </c>
+      <c r="G65" t="n">
         <v>36.7981</v>
       </c>
-      <c r="G65" t="n">
+      <c r="H65" t="n">
         <v>58.0509</v>
       </c>
     </row>
@@ -2332,9 +2529,12 @@
         <v>0.8915</v>
       </c>
       <c r="F66" t="n">
+        <v>1.7477</v>
+      </c>
+      <c r="G66" t="n">
         <v>34.3183</v>
       </c>
-      <c r="G66" t="n">
+      <c r="H66" t="n">
         <v>56.6655</v>
       </c>
     </row>
@@ -2361,9 +2561,12 @@
         <v>0.8774</v>
       </c>
       <c r="F67" t="n">
+        <v>1.7556</v>
+      </c>
+      <c r="G67" t="n">
         <v>36.1072</v>
       </c>
-      <c r="G67" t="n">
+      <c r="H67" t="n">
         <v>56.9639</v>
       </c>
     </row>
@@ -2390,9 +2593,12 @@
         <v>0.9131</v>
       </c>
       <c r="F68" t="n">
+        <v>1.7523</v>
+      </c>
+      <c r="G68" t="n">
         <v>31.0511</v>
       </c>
-      <c r="G68" t="n">
+      <c r="H68" t="n">
         <v>56.8406</v>
       </c>
     </row>
@@ -2419,9 +2625,12 @@
         <v>0.9555</v>
       </c>
       <c r="F69" t="n">
+        <v>1.4308</v>
+      </c>
+      <c r="G69" t="n">
         <v>20.6827</v>
       </c>
-      <c r="G69" t="n">
+      <c r="H69" t="n">
         <v>43.0133</v>
       </c>
     </row>
@@ -2448,9 +2657,12 @@
         <v>0.9311</v>
       </c>
       <c r="F70" t="n">
+        <v>1.4264</v>
+      </c>
+      <c r="G70" t="n">
         <v>24.8029</v>
       </c>
-      <c r="G70" t="n">
+      <c r="H70" t="n">
         <v>42.7936</v>
       </c>
     </row>
@@ -2477,9 +2689,12 @@
         <v>0.9752999999999999</v>
       </c>
       <c r="F71" t="n">
+        <v>1.4327</v>
+      </c>
+      <c r="G71" t="n">
         <v>15.3741</v>
       </c>
-      <c r="G71" t="n">
+      <c r="H71" t="n">
         <v>43.1087</v>
       </c>
     </row>
@@ -2506,9 +2721,12 @@
         <v>0.9498</v>
       </c>
       <c r="F72" t="n">
+        <v>1.4335</v>
+      </c>
+      <c r="G72" t="n">
         <v>21.3599</v>
       </c>
-      <c r="G72" t="n">
+      <c r="H72" t="n">
         <v>43.1493</v>
       </c>
     </row>
@@ -2535,9 +2753,12 @@
         <v>0.9673</v>
       </c>
       <c r="F73" t="n">
+        <v>1.445</v>
+      </c>
+      <c r="G73" t="n">
         <v>18.6537</v>
       </c>
-      <c r="G73" t="n">
+      <c r="H73" t="n">
         <v>43.7181</v>
       </c>
     </row>
@@ -2564,9 +2785,12 @@
         <v>0.9366</v>
       </c>
       <c r="F74" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="G74" t="n">
         <v>24.5659</v>
       </c>
-      <c r="G74" t="n">
+      <c r="H74" t="n">
         <v>43.5693</v>
       </c>
     </row>
@@ -2593,9 +2817,12 @@
         <v>0.9305</v>
       </c>
       <c r="F75" t="n">
+        <v>1.4567</v>
+      </c>
+      <c r="G75" t="n">
         <v>24.7148</v>
       </c>
-      <c r="G75" t="n">
+      <c r="H75" t="n">
         <v>44.2871</v>
       </c>
     </row>
@@ -2622,9 +2849,12 @@
         <v>0.9305</v>
       </c>
       <c r="F76" t="n">
+        <v>1.4567</v>
+      </c>
+      <c r="G76" t="n">
         <v>24.7148</v>
       </c>
-      <c r="G76" t="n">
+      <c r="H76" t="n">
         <v>44.2871</v>
       </c>
     </row>
@@ -2651,9 +2881,12 @@
         <v>0.8699</v>
       </c>
       <c r="F77" t="n">
+        <v>1.7726</v>
+      </c>
+      <c r="G77" t="n">
         <v>36.0165</v>
       </c>
-      <c r="G77" t="n">
+      <c r="H77" t="n">
         <v>57.6014</v>
       </c>
     </row>
@@ -2680,9 +2913,12 @@
         <v>0.8809</v>
       </c>
       <c r="F78" t="n">
+        <v>1.7687</v>
+      </c>
+      <c r="G78" t="n">
         <v>34.2671</v>
       </c>
-      <c r="G78" t="n">
+      <c r="H78" t="n">
         <v>57.4587</v>
       </c>
     </row>
@@ -2709,9 +2945,12 @@
         <v>0.9379999999999999</v>
       </c>
       <c r="F79" t="n">
+        <v>1.7691</v>
+      </c>
+      <c r="G79" t="n">
         <v>26.6891</v>
       </c>
-      <c r="G79" t="n">
+      <c r="H79" t="n">
         <v>57.4727</v>
       </c>
     </row>
@@ -2738,9 +2977,12 @@
         <v>0.8809</v>
       </c>
       <c r="F80" t="n">
+        <v>1.7684</v>
+      </c>
+      <c r="G80" t="n">
         <v>34.2684</v>
       </c>
-      <c r="G80" t="n">
+      <c r="H80" t="n">
         <v>57.4455</v>
       </c>
     </row>
@@ -2767,9 +3009,12 @@
         <v>0.8505</v>
       </c>
       <c r="F81" t="n">
+        <v>1.7478</v>
+      </c>
+      <c r="G81" t="n">
         <v>38.0116</v>
       </c>
-      <c r="G81" t="n">
+      <c r="H81" t="n">
         <v>56.6721</v>
       </c>
     </row>
@@ -2796,9 +3041,12 @@
         <v>0.8473000000000001</v>
       </c>
       <c r="F82" t="n">
+        <v>1.7568</v>
+      </c>
+      <c r="G82" t="n">
         <v>38.2528</v>
       </c>
-      <c r="G82" t="n">
+      <c r="H82" t="n">
         <v>57.0092</v>
       </c>
     </row>
@@ -2825,9 +3073,12 @@
         <v>0.93</v>
       </c>
       <c r="F83" t="n">
+        <v>1.4543</v>
+      </c>
+      <c r="G83" t="n">
         <v>24.7672</v>
       </c>
-      <c r="G83" t="n">
+      <c r="H83" t="n">
         <v>44.1722</v>
       </c>
     </row>
@@ -2854,9 +3105,12 @@
         <v>0.9308</v>
       </c>
       <c r="F84" t="n">
+        <v>1.4548</v>
+      </c>
+      <c r="G84" t="n">
         <v>24.6533</v>
       </c>
-      <c r="G84" t="n">
+      <c r="H84" t="n">
         <v>44.1975</v>
       </c>
     </row>
@@ -2883,9 +3137,12 @@
         <v>0.9301</v>
       </c>
       <c r="F85" t="n">
+        <v>1.4548</v>
+      </c>
+      <c r="G85" t="n">
         <v>24.7593</v>
       </c>
-      <c r="G85" t="n">
+      <c r="H85" t="n">
         <v>44.1949</v>
       </c>
     </row>
@@ -2912,9 +3169,12 @@
         <v>0.964</v>
       </c>
       <c r="F86" t="n">
+        <v>1.3958</v>
+      </c>
+      <c r="G86" t="n">
         <v>18.7919</v>
       </c>
-      <c r="G86" t="n">
+      <c r="H86" t="n">
         <v>41.2281</v>
       </c>
     </row>
@@ -2941,9 +3201,12 @@
         <v>0.95</v>
       </c>
       <c r="F87" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G87" t="n">
         <v>21.3739</v>
       </c>
-      <c r="G87" t="n">
+      <c r="H87" t="n">
         <v>41.4478</v>
       </c>
     </row>
@@ -2970,9 +3233,12 @@
         <v>0.9537</v>
       </c>
       <c r="F88" t="n">
+        <v>1.4098</v>
+      </c>
+      <c r="G88" t="n">
         <v>21.0797</v>
       </c>
-      <c r="G88" t="n">
+      <c r="H88" t="n">
         <v>41.9511</v>
       </c>
     </row>
@@ -2999,9 +3265,12 @@
         <v>0.9351</v>
       </c>
       <c r="F89" t="n">
+        <v>1.4073</v>
+      </c>
+      <c r="G89" t="n">
         <v>24.4372</v>
       </c>
-      <c r="G89" t="n">
+      <c r="H89" t="n">
         <v>41.8251</v>
       </c>
     </row>
@@ -3028,9 +3297,12 @@
         <v>0.9447</v>
       </c>
       <c r="F90" t="n">
+        <v>1.3846</v>
+      </c>
+      <c r="G90" t="n">
         <v>23.2666</v>
       </c>
-      <c r="G90" t="n">
+      <c r="H90" t="n">
         <v>40.6393</v>
       </c>
     </row>
@@ -3057,9 +3329,12 @@
         <v>0.9475</v>
       </c>
       <c r="F91" t="n">
+        <v>1.3723</v>
+      </c>
+      <c r="G91" t="n">
         <v>22.4672</v>
       </c>
-      <c r="G91" t="n">
+      <c r="H91" t="n">
         <v>39.9884</v>
       </c>
     </row>
@@ -3086,9 +3361,12 @@
         <v>0.9537</v>
       </c>
       <c r="F92" t="n">
+        <v>1.4098</v>
+      </c>
+      <c r="G92" t="n">
         <v>21.0797</v>
       </c>
-      <c r="G92" t="n">
+      <c r="H92" t="n">
         <v>41.9511</v>
       </c>
     </row>
@@ -3115,9 +3393,12 @@
         <v>0.9475</v>
       </c>
       <c r="F93" t="n">
+        <v>1.3723</v>
+      </c>
+      <c r="G93" t="n">
         <v>22.4672</v>
       </c>
-      <c r="G93" t="n">
+      <c r="H93" t="n">
         <v>39.9884</v>
       </c>
     </row>
@@ -3144,9 +3425,12 @@
         <v>0.9265</v>
       </c>
       <c r="F94" t="n">
+        <v>1.4451</v>
+      </c>
+      <c r="G94" t="n">
         <v>25.6773</v>
       </c>
-      <c r="G94" t="n">
+      <c r="H94" t="n">
         <v>43.7205</v>
       </c>
     </row>
@@ -3173,9 +3457,12 @@
         <v>0.7848000000000001</v>
       </c>
       <c r="F95" t="n">
+        <v>2.0905</v>
+      </c>
+      <c r="G95" t="n">
         <v>47.1317</v>
       </c>
-      <c r="G95" t="n">
+      <c r="H95" t="n">
         <v>68.43519999999999</v>
       </c>
     </row>
@@ -3202,9 +3489,12 @@
         <v>0.9268999999999999</v>
       </c>
       <c r="F96" t="n">
+        <v>1.442</v>
+      </c>
+      <c r="G96" t="n">
         <v>25.5813</v>
       </c>
-      <c r="G96" t="n">
+      <c r="H96" t="n">
         <v>43.5663</v>
       </c>
     </row>
@@ -3231,9 +3521,12 @@
         <v>0.9265</v>
       </c>
       <c r="F97" t="n">
+        <v>1.4427</v>
+      </c>
+      <c r="G97" t="n">
         <v>25.6296</v>
       </c>
-      <c r="G97" t="n">
+      <c r="H97" t="n">
         <v>43.6045</v>
       </c>
     </row>
@@ -3260,9 +3553,12 @@
         <v>0.9474</v>
       </c>
       <c r="F98" t="n">
+        <v>1.3771</v>
+      </c>
+      <c r="G98" t="n">
         <v>22.5343</v>
       </c>
-      <c r="G98" t="n">
+      <c r="H98" t="n">
         <v>40.2419</v>
       </c>
     </row>
@@ -3289,9 +3585,12 @@
         <v>0.9635</v>
       </c>
       <c r="F99" t="n">
+        <v>1.3797</v>
+      </c>
+      <c r="G99" t="n">
         <v>19.3477</v>
       </c>
-      <c r="G99" t="n">
+      <c r="H99" t="n">
         <v>40.3837</v>
       </c>
     </row>
@@ -3311,16 +3610,19 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9312</v>
+        <v>0.9314</v>
       </c>
       <c r="F100" t="n">
-        <v>25.322</v>
+        <v>1.3793</v>
       </c>
       <c r="G100" t="n">
+        <v>25.3157</v>
+      </c>
+      <c r="H100" t="n">
         <v>40.3612</v>
       </c>
     </row>
@@ -3347,9 +3649,12 @@
         <v>0.9618</v>
       </c>
       <c r="F101" t="n">
+        <v>1.3781</v>
+      </c>
+      <c r="G101" t="n">
         <v>19.6167</v>
       </c>
-      <c r="G101" t="n">
+      <c r="H101" t="n">
         <v>40.2966</v>
       </c>
     </row>
@@ -3376,9 +3681,12 @@
         <v>0.9389999999999999</v>
       </c>
       <c r="F102" t="n">
+        <v>1.3807</v>
+      </c>
+      <c r="G102" t="n">
         <v>23.631</v>
       </c>
-      <c r="G102" t="n">
+      <c r="H102" t="n">
         <v>40.4327</v>
       </c>
     </row>
@@ -3405,9 +3713,12 @@
         <v>0.9757</v>
       </c>
       <c r="F103" t="n">
+        <v>1.3698</v>
+      </c>
+      <c r="G103" t="n">
         <v>16.1569</v>
       </c>
-      <c r="G103" t="n">
+      <c r="H103" t="n">
         <v>39.8523</v>
       </c>
     </row>
@@ -3434,9 +3745,12 @@
         <v>0.9372</v>
       </c>
       <c r="F104" t="n">
+        <v>1.389</v>
+      </c>
+      <c r="G104" t="n">
         <v>24.6145</v>
       </c>
-      <c r="G104" t="n">
+      <c r="H104" t="n">
         <v>40.8747</v>
       </c>
     </row>
@@ -3463,9 +3777,12 @@
         <v>0.9666</v>
       </c>
       <c r="F105" t="n">
+        <v>1.3877</v>
+      </c>
+      <c r="G105" t="n">
         <v>18.7989</v>
       </c>
-      <c r="G105" t="n">
+      <c r="H105" t="n">
         <v>40.8068</v>
       </c>
     </row>
@@ -3492,9 +3809,12 @@
         <v>0.9342</v>
       </c>
       <c r="F106" t="n">
+        <v>1.3808</v>
+      </c>
+      <c r="G106" t="n">
         <v>25.0083</v>
       </c>
-      <c r="G106" t="n">
+      <c r="H106" t="n">
         <v>40.4422</v>
       </c>
     </row>
@@ -3521,9 +3841,12 @@
         <v>0.9772</v>
       </c>
       <c r="F107" t="n">
+        <v>1.3806</v>
+      </c>
+      <c r="G107" t="n">
         <v>15.4265</v>
       </c>
-      <c r="G107" t="n">
+      <c r="H107" t="n">
         <v>40.4295</v>
       </c>
     </row>
@@ -3550,9 +3873,12 @@
         <v>0.9349</v>
       </c>
       <c r="F108" t="n">
+        <v>1.4547</v>
+      </c>
+      <c r="G108" t="n">
         <v>25.4454</v>
       </c>
-      <c r="G108" t="n">
+      <c r="H108" t="n">
         <v>44.1909</v>
       </c>
     </row>
@@ -3572,16 +3898,19 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E109" t="n">
         <v>0.9381</v>
       </c>
       <c r="F109" t="n">
-        <v>24.7831</v>
+        <v>1.4471</v>
       </c>
       <c r="G109" t="n">
+        <v>24.783</v>
+      </c>
+      <c r="H109" t="n">
         <v>43.8199</v>
       </c>
     </row>
@@ -3608,9 +3937,12 @@
         <v>0.9811</v>
       </c>
       <c r="F110" t="n">
+        <v>1.4432</v>
+      </c>
+      <c r="G110" t="n">
         <v>15.1634</v>
       </c>
-      <c r="G110" t="n">
+      <c r="H110" t="n">
         <v>43.6275</v>
       </c>
     </row>
@@ -3637,9 +3969,12 @@
         <v>0.9821</v>
       </c>
       <c r="F111" t="n">
+        <v>1.4185</v>
+      </c>
+      <c r="G111" t="n">
         <v>14.5135</v>
       </c>
-      <c r="G111" t="n">
+      <c r="H111" t="n">
         <v>42.3931</v>
       </c>
     </row>
@@ -3666,9 +4001,12 @@
         <v>0.9362</v>
       </c>
       <c r="F112" t="n">
+        <v>1.4547</v>
+      </c>
+      <c r="G112" t="n">
         <v>25.222</v>
       </c>
-      <c r="G112" t="n">
+      <c r="H112" t="n">
         <v>44.1881</v>
       </c>
     </row>
@@ -3695,9 +4033,12 @@
         <v>0.9385</v>
       </c>
       <c r="F113" t="n">
+        <v>1.4481</v>
+      </c>
+      <c r="G113" t="n">
         <v>24.7706</v>
       </c>
-      <c r="G113" t="n">
+      <c r="H113" t="n">
         <v>43.8706</v>
       </c>
     </row>
@@ -3724,9 +4065,12 @@
         <v>0.9811</v>
       </c>
       <c r="F114" t="n">
+        <v>1.4426</v>
+      </c>
+      <c r="G114" t="n">
         <v>15.1581</v>
       </c>
-      <c r="G114" t="n">
+      <c r="H114" t="n">
         <v>43.6001</v>
       </c>
     </row>
@@ -3753,9 +4097,12 @@
         <v>0.9817</v>
       </c>
       <c r="F115" t="n">
+        <v>1.4215</v>
+      </c>
+      <c r="G115" t="n">
         <v>14.6775</v>
       </c>
-      <c r="G115" t="n">
+      <c r="H115" t="n">
         <v>42.5479</v>
       </c>
     </row>
@@ -3782,9 +4129,12 @@
         <v>0.8248</v>
       </c>
       <c r="F116" t="n">
+        <v>1.7971</v>
+      </c>
+      <c r="G116" t="n">
         <v>40.6032</v>
       </c>
-      <c r="G116" t="n">
+      <c r="H116" t="n">
         <v>58.5079</v>
       </c>
     </row>
@@ -3811,9 +4161,12 @@
         <v>0.8242</v>
       </c>
       <c r="F117" t="n">
+        <v>1.7932</v>
+      </c>
+      <c r="G117" t="n">
         <v>40.6691</v>
       </c>
-      <c r="G117" t="n">
+      <c r="H117" t="n">
         <v>58.3656</v>
       </c>
     </row>
@@ -3840,9 +4193,12 @@
         <v>0.9666</v>
       </c>
       <c r="F118" t="n">
+        <v>1.3877</v>
+      </c>
+      <c r="G118" t="n">
         <v>18.7989</v>
       </c>
-      <c r="G118" t="n">
+      <c r="H118" t="n">
         <v>40.8068</v>
       </c>
     </row>
@@ -3862,16 +4218,19 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
         <v>0.9385</v>
       </c>
       <c r="F119" t="n">
-        <v>24.7705</v>
+        <v>1.4481</v>
       </c>
       <c r="G119" t="n">
+        <v>24.7706</v>
+      </c>
+      <c r="H119" t="n">
         <v>43.8706</v>
       </c>
     </row>
@@ -3898,9 +4257,12 @@
         <v>0.9332</v>
       </c>
       <c r="F120" t="n">
+        <v>1.5021</v>
+      </c>
+      <c r="G120" t="n">
         <v>24.5573</v>
       </c>
-      <c r="G120" t="n">
+      <c r="H120" t="n">
         <v>46.4371</v>
       </c>
     </row>
@@ -3927,9 +4289,12 @@
         <v>0.9332</v>
       </c>
       <c r="F121" t="n">
+        <v>1.5021</v>
+      </c>
+      <c r="G121" t="n">
         <v>24.5573</v>
       </c>
-      <c r="G121" t="n">
+      <c r="H121" t="n">
         <v>46.4371</v>
       </c>
     </row>
@@ -3956,9 +4321,12 @@
         <v>0.9327</v>
       </c>
       <c r="F122" t="n">
+        <v>1.4002</v>
+      </c>
+      <c r="G122" t="n">
         <v>24.2758</v>
       </c>
-      <c r="G122" t="n">
+      <c r="H122" t="n">
         <v>41.4573</v>
       </c>
     </row>
@@ -3985,9 +4353,12 @@
         <v>0.9384</v>
       </c>
       <c r="F123" t="n">
+        <v>1.4484</v>
+      </c>
+      <c r="G123" t="n">
         <v>24.7904</v>
       </c>
-      <c r="G123" t="n">
+      <c r="H123" t="n">
         <v>43.8808</v>
       </c>
     </row>
@@ -4014,9 +4385,12 @@
         <v>0.9804</v>
       </c>
       <c r="F124" t="n">
+        <v>1.4454</v>
+      </c>
+      <c r="G124" t="n">
         <v>16.0758</v>
       </c>
-      <c r="G124" t="n">
+      <c r="H124" t="n">
         <v>43.7372</v>
       </c>
     </row>
@@ -4043,9 +4417,12 @@
         <v>0.9766</v>
       </c>
       <c r="F125" t="n">
+        <v>1.4439</v>
+      </c>
+      <c r="G125" t="n">
         <v>15.6321</v>
       </c>
-      <c r="G125" t="n">
+      <c r="H125" t="n">
         <v>43.6614</v>
       </c>
     </row>
@@ -4065,16 +4442,19 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
         <v>0.9374</v>
       </c>
       <c r="F126" t="n">
+        <v>1.4095</v>
+      </c>
+      <c r="G126" t="n">
         <v>23.8029</v>
       </c>
-      <c r="G126" t="n">
+      <c r="H126" t="n">
         <v>41.9383</v>
       </c>
     </row>
@@ -4101,9 +4481,12 @@
         <v>0.8128</v>
       </c>
       <c r="F127" t="n">
+        <v>1.8364</v>
+      </c>
+      <c r="G127" t="n">
         <v>41.2129</v>
       </c>
-      <c r="G127" t="n">
+      <c r="H127" t="n">
         <v>59.9333</v>
       </c>
     </row>
@@ -4130,9 +4513,12 @@
         <v>0.9598</v>
       </c>
       <c r="F128" t="n">
+        <v>1.4065</v>
+      </c>
+      <c r="G128" t="n">
         <v>19.6326</v>
       </c>
-      <c r="G128" t="n">
+      <c r="H128" t="n">
         <v>41.7819</v>
       </c>
     </row>
@@ -4159,9 +4545,12 @@
         <v>0.968</v>
       </c>
       <c r="F129" t="n">
+        <v>1.4073</v>
+      </c>
+      <c r="G129" t="n">
         <v>17.451</v>
       </c>
-      <c r="G129" t="n">
+      <c r="H129" t="n">
         <v>41.8212</v>
       </c>
     </row>
@@ -4188,9 +4577,12 @@
         <v>0.9613</v>
       </c>
       <c r="F130" t="n">
+        <v>1.4074</v>
+      </c>
+      <c r="G130" t="n">
         <v>19.4069</v>
       </c>
-      <c r="G130" t="n">
+      <c r="H130" t="n">
         <v>41.8309</v>
       </c>
     </row>
@@ -4217,9 +4609,12 @@
         <v>0.9613</v>
       </c>
       <c r="F131" t="n">
+        <v>1.4031</v>
+      </c>
+      <c r="G131" t="n">
         <v>19.4316</v>
       </c>
-      <c r="G131" t="n">
+      <c r="H131" t="n">
         <v>41.6089</v>
       </c>
     </row>
@@ -4246,9 +4641,12 @@
         <v>0.9684</v>
       </c>
       <c r="F132" t="n">
+        <v>1.4044</v>
+      </c>
+      <c r="G132" t="n">
         <v>17.3323</v>
       </c>
-      <c r="G132" t="n">
+      <c r="H132" t="n">
         <v>41.6724</v>
       </c>
     </row>
@@ -4275,9 +4673,12 @@
         <v>0.9686</v>
       </c>
       <c r="F133" t="n">
+        <v>1.4066</v>
+      </c>
+      <c r="G133" t="n">
         <v>17.3021</v>
       </c>
-      <c r="G133" t="n">
+      <c r="H133" t="n">
         <v>41.7896</v>
       </c>
     </row>
@@ -4304,9 +4705,12 @@
         <v>0.9797</v>
       </c>
       <c r="F134" t="n">
+        <v>1.4057</v>
+      </c>
+      <c r="G134" t="n">
         <v>14.6209</v>
       </c>
-      <c r="G134" t="n">
+      <c r="H134" t="n">
         <v>41.7437</v>
       </c>
     </row>
@@ -4333,9 +4737,12 @@
         <v>0.96</v>
       </c>
       <c r="F135" t="n">
+        <v>1.406</v>
+      </c>
+      <c r="G135" t="n">
         <v>19.5844</v>
       </c>
-      <c r="G135" t="n">
+      <c r="H135" t="n">
         <v>41.7565</v>
       </c>
     </row>
@@ -4362,9 +4769,12 @@
         <v>0.968</v>
       </c>
       <c r="F136" t="n">
+        <v>1.404</v>
+      </c>
+      <c r="G136" t="n">
         <v>17.4409</v>
       </c>
-      <c r="G136" t="n">
+      <c r="H136" t="n">
         <v>41.6549</v>
       </c>
     </row>
@@ -4391,9 +4801,12 @@
         <v>0.9757</v>
       </c>
       <c r="F137" t="n">
+        <v>1.3586</v>
+      </c>
+      <c r="G137" t="n">
         <v>15.276</v>
       </c>
-      <c r="G137" t="n">
+      <c r="H137" t="n">
         <v>39.2445</v>
       </c>
     </row>
@@ -4420,9 +4833,12 @@
         <v>0.9761</v>
       </c>
       <c r="F138" t="n">
+        <v>1.3648</v>
+      </c>
+      <c r="G138" t="n">
         <v>15.6221</v>
       </c>
-      <c r="G138" t="n">
+      <c r="H138" t="n">
         <v>39.5832</v>
       </c>
     </row>
@@ -4449,9 +4865,12 @@
         <v>0.9278999999999999</v>
       </c>
       <c r="F139" t="n">
+        <v>1.3662</v>
+      </c>
+      <c r="G139" t="n">
         <v>24.931</v>
       </c>
-      <c r="G139" t="n">
+      <c r="H139" t="n">
         <v>39.6549</v>
       </c>
     </row>
@@ -4478,9 +4897,12 @@
         <v>0.9472</v>
       </c>
       <c r="F140" t="n">
+        <v>1.3613</v>
+      </c>
+      <c r="G140" t="n">
         <v>22.3945</v>
       </c>
-      <c r="G140" t="n">
+      <c r="H140" t="n">
         <v>39.3913</v>
       </c>
     </row>
@@ -4507,9 +4929,12 @@
         <v>0.9298</v>
       </c>
       <c r="F141" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G141" t="n">
         <v>25.806</v>
       </c>
-      <c r="G141" t="n">
+      <c r="H141" t="n">
         <v>39.8611</v>
       </c>
     </row>
@@ -4536,9 +4961,12 @@
         <v>0.9761</v>
       </c>
       <c r="F142" t="n">
+        <v>1.3648</v>
+      </c>
+      <c r="G142" t="n">
         <v>15.6221</v>
       </c>
-      <c r="G142" t="n">
+      <c r="H142" t="n">
         <v>39.5832</v>
       </c>
     </row>
@@ -4565,9 +4993,12 @@
         <v>0.9313</v>
       </c>
       <c r="F143" t="n">
+        <v>1.3665</v>
+      </c>
+      <c r="G143" t="n">
         <v>24.4046</v>
       </c>
-      <c r="G143" t="n">
+      <c r="H143" t="n">
         <v>39.6758</v>
       </c>
     </row>
@@ -4594,9 +5025,12 @@
         <v>0.9313</v>
       </c>
       <c r="F144" t="n">
+        <v>1.3682</v>
+      </c>
+      <c r="G144" t="n">
         <v>24.4502</v>
       </c>
-      <c r="G144" t="n">
+      <c r="H144" t="n">
         <v>39.7665</v>
       </c>
     </row>
@@ -4623,9 +5057,12 @@
         <v>0.9298</v>
       </c>
       <c r="F145" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G145" t="n">
         <v>25.806</v>
       </c>
-      <c r="G145" t="n">
+      <c r="H145" t="n">
         <v>39.8611</v>
       </c>
     </row>
@@ -4652,9 +5089,12 @@
         <v>0.8117</v>
       </c>
       <c r="F146" t="n">
+        <v>1.8337</v>
+      </c>
+      <c r="G146" t="n">
         <v>41.2649</v>
       </c>
-      <c r="G146" t="n">
+      <c r="H146" t="n">
         <v>59.8362</v>
       </c>
     </row>
@@ -4681,9 +5121,12 @@
         <v>0.8117</v>
       </c>
       <c r="F147" t="n">
+        <v>1.8329</v>
+      </c>
+      <c r="G147" t="n">
         <v>41.2352</v>
       </c>
-      <c r="G147" t="n">
+      <c r="H147" t="n">
         <v>59.8089</v>
       </c>
     </row>
@@ -4710,9 +5153,12 @@
         <v>0.8117</v>
       </c>
       <c r="F148" t="n">
+        <v>1.8345</v>
+      </c>
+      <c r="G148" t="n">
         <v>41.1723</v>
       </c>
-      <c r="G148" t="n">
+      <c r="H148" t="n">
         <v>59.8646</v>
       </c>
     </row>
@@ -4739,9 +5185,12 @@
         <v>0.8129</v>
       </c>
       <c r="F149" t="n">
+        <v>1.8352</v>
+      </c>
+      <c r="G149" t="n">
         <v>41.0549</v>
       </c>
-      <c r="G149" t="n">
+      <c r="H149" t="n">
         <v>59.8899</v>
       </c>
     </row>
@@ -4768,9 +5217,12 @@
         <v>0.8131</v>
       </c>
       <c r="F150" t="n">
+        <v>1.8369</v>
+      </c>
+      <c r="G150" t="n">
         <v>41.1718</v>
       </c>
-      <c r="G150" t="n">
+      <c r="H150" t="n">
         <v>59.9506</v>
       </c>
     </row>
@@ -4797,9 +5249,12 @@
         <v>0.8131</v>
       </c>
       <c r="F151" t="n">
+        <v>1.8358</v>
+      </c>
+      <c r="G151" t="n">
         <v>41.1741</v>
       </c>
-      <c r="G151" t="n">
+      <c r="H151" t="n">
         <v>59.9109</v>
       </c>
     </row>
@@ -4826,9 +5281,12 @@
         <v>0.8147</v>
       </c>
       <c r="F152" t="n">
+        <v>1.8367</v>
+      </c>
+      <c r="G152" t="n">
         <v>41.086</v>
       </c>
-      <c r="G152" t="n">
+      <c r="H152" t="n">
         <v>59.9441</v>
       </c>
     </row>
@@ -4855,9 +5313,12 @@
         <v>0.8139999999999999</v>
       </c>
       <c r="F153" t="n">
+        <v>1.8368</v>
+      </c>
+      <c r="G153" t="n">
         <v>41.1103</v>
       </c>
-      <c r="G153" t="n">
+      <c r="H153" t="n">
         <v>59.9469</v>
       </c>
     </row>
@@ -4884,9 +5345,12 @@
         <v>0.8106</v>
       </c>
       <c r="F154" t="n">
+        <v>1.8392</v>
+      </c>
+      <c r="G154" t="n">
         <v>41.3209</v>
       </c>
-      <c r="G154" t="n">
+      <c r="H154" t="n">
         <v>60.0346</v>
       </c>
     </row>
@@ -4913,9 +5377,12 @@
         <v>0.8310999999999999</v>
       </c>
       <c r="F155" t="n">
+        <v>1.8014</v>
+      </c>
+      <c r="G155" t="n">
         <v>39.6303</v>
       </c>
-      <c r="G155" t="n">
+      <c r="H155" t="n">
         <v>58.6658</v>
       </c>
     </row>
@@ -4942,9 +5409,12 @@
         <v>0.8331</v>
       </c>
       <c r="F156" t="n">
+        <v>1.8078</v>
+      </c>
+      <c r="G156" t="n">
         <v>39.4958</v>
       </c>
-      <c r="G156" t="n">
+      <c r="H156" t="n">
         <v>58.8995</v>
       </c>
     </row>
@@ -4971,9 +5441,12 @@
         <v>0.8336</v>
       </c>
       <c r="F157" t="n">
+        <v>1.8116</v>
+      </c>
+      <c r="G157" t="n">
         <v>39.3823</v>
       </c>
-      <c r="G157" t="n">
+      <c r="H157" t="n">
         <v>59.0369</v>
       </c>
     </row>
@@ -5000,9 +5473,12 @@
         <v>0.8366</v>
       </c>
       <c r="F158" t="n">
+        <v>1.7551</v>
+      </c>
+      <c r="G158" t="n">
         <v>39.4645</v>
       </c>
-      <c r="G158" t="n">
+      <c r="H158" t="n">
         <v>56.9446</v>
       </c>
     </row>
@@ -5029,9 +5505,12 @@
         <v>0.9736</v>
       </c>
       <c r="F159" t="n">
+        <v>1.421</v>
+      </c>
+      <c r="G159" t="n">
         <v>16.0301</v>
       </c>
-      <c r="G159" t="n">
+      <c r="H159" t="n">
         <v>42.5221</v>
       </c>
     </row>
@@ -5058,9 +5537,12 @@
         <v>0.8164</v>
       </c>
       <c r="F160" t="n">
+        <v>1.809</v>
+      </c>
+      <c r="G160" t="n">
         <v>40.775</v>
       </c>
-      <c r="G160" t="n">
+      <c r="H160" t="n">
         <v>58.9446</v>
       </c>
     </row>
@@ -5087,9 +5569,12 @@
         <v>0.8146</v>
       </c>
       <c r="F161" t="n">
+        <v>1.8098</v>
+      </c>
+      <c r="G161" t="n">
         <v>40.8601</v>
       </c>
-      <c r="G161" t="n">
+      <c r="H161" t="n">
         <v>58.9743</v>
       </c>
     </row>
@@ -5116,9 +5601,12 @@
         <v>0.9752</v>
       </c>
       <c r="F162" t="n">
+        <v>1.4268</v>
+      </c>
+      <c r="G162" t="n">
         <v>15.5208</v>
       </c>
-      <c r="G162" t="n">
+      <c r="H162" t="n">
         <v>42.8121</v>
       </c>
     </row>
@@ -5145,9 +5633,12 @@
         <v>0.9386</v>
       </c>
       <c r="F163" t="n">
+        <v>1.3742</v>
+      </c>
+      <c r="G163" t="n">
         <v>23.2084</v>
       </c>
-      <c r="G163" t="n">
+      <c r="H163" t="n">
         <v>40.0892</v>
       </c>
     </row>
@@ -5174,9 +5665,12 @@
         <v>0.98</v>
       </c>
       <c r="F164" t="n">
+        <v>1.3598</v>
+      </c>
+      <c r="G164" t="n">
         <v>14.6251</v>
       </c>
-      <c r="G164" t="n">
+      <c r="H164" t="n">
         <v>39.3099</v>
       </c>
     </row>
@@ -5203,9 +5697,12 @@
         <v>0.9766</v>
       </c>
       <c r="F165" t="n">
+        <v>1.4439</v>
+      </c>
+      <c r="G165" t="n">
         <v>15.6321</v>
       </c>
-      <c r="G165" t="n">
+      <c r="H165" t="n">
         <v>43.6614</v>
       </c>
     </row>
@@ -5232,9 +5729,12 @@
         <v>0.8994</v>
       </c>
       <c r="F166" t="n">
+        <v>2.0873</v>
+      </c>
+      <c r="G166" t="n">
         <v>34.6214</v>
       </c>
-      <c r="G166" t="n">
+      <c r="H166" t="n">
         <v>68.3343</v>
       </c>
     </row>
@@ -5254,16 +5754,19 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
         <v>0.9317</v>
       </c>
       <c r="F167" t="n">
-        <v>24.5121</v>
+        <v>1.3668</v>
       </c>
       <c r="G167" t="n">
+        <v>24.5118</v>
+      </c>
+      <c r="H167" t="n">
         <v>39.6886</v>
       </c>
     </row>
@@ -5290,9 +5793,12 @@
         <v>0.9391</v>
       </c>
       <c r="F168" t="n">
+        <v>1.3635</v>
+      </c>
+      <c r="G168" t="n">
         <v>24.3951</v>
       </c>
-      <c r="G168" t="n">
+      <c r="H168" t="n">
         <v>39.5112</v>
       </c>
     </row>
@@ -5319,9 +5825,12 @@
         <v>0.9504</v>
       </c>
       <c r="F169" t="n">
+        <v>1.3994</v>
+      </c>
+      <c r="G169" t="n">
         <v>21.2894</v>
       </c>
-      <c r="G169" t="n">
+      <c r="H169" t="n">
         <v>41.4185</v>
       </c>
     </row>
@@ -5348,9 +5857,12 @@
         <v>0.9556</v>
       </c>
       <c r="F170" t="n">
+        <v>1.4349</v>
+      </c>
+      <c r="G170" t="n">
         <v>20.9823</v>
       </c>
-      <c r="G170" t="n">
+      <c r="H170" t="n">
         <v>43.2193</v>
       </c>
     </row>
@@ -5377,9 +5889,12 @@
         <v>0.9444</v>
       </c>
       <c r="F171" t="n">
+        <v>1.3842</v>
+      </c>
+      <c r="G171" t="n">
         <v>23.233</v>
       </c>
-      <c r="G171" t="n">
+      <c r="H171" t="n">
         <v>40.6209</v>
       </c>
     </row>
@@ -5406,9 +5921,12 @@
         <v>0.9385</v>
       </c>
       <c r="F172" t="n">
+        <v>1.3677</v>
+      </c>
+      <c r="G172" t="n">
         <v>23.5341</v>
       </c>
-      <c r="G172" t="n">
+      <c r="H172" t="n">
         <v>39.738</v>
       </c>
     </row>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X9.cis.beta.carotene/RANDOMSEARCH_DETAILS_X9.cis.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X9.cis.beta.carotene/RANDOMSEARCH_DETAILS_X9.cis.beta.carotene.xlsx
@@ -478,16 +478,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.9559</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3991</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>20.1046</v>
+        <v>21.8823</v>
       </c>
       <c r="H2" t="n">
-        <v>41.4024</v>
+        <v>44.601</v>
       </c>
     </row>
     <row r="3">
@@ -506,20 +506,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.9699</v>
+        <v>0.9516</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3937</v>
+        <v>0.5779</v>
       </c>
       <c r="G3" t="n">
-        <v>17.1809</v>
+        <v>21.3353</v>
       </c>
       <c r="H3" t="n">
-        <v>41.1195</v>
+        <v>42.6692</v>
       </c>
     </row>
     <row r="4">
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9265</v>
+        <v>0.9169</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4451</v>
+        <v>0.503</v>
       </c>
       <c r="G4" t="n">
-        <v>25.6773</v>
+        <v>27.2423</v>
       </c>
       <c r="H4" t="n">
-        <v>43.7205</v>
+        <v>46.2989</v>
       </c>
     </row>
     <row r="5">
@@ -570,20 +570,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.8629</v>
+        <v>0.8221000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7908</v>
+        <v>0.0896</v>
       </c>
       <c r="G5" t="n">
-        <v>36.8947</v>
+        <v>40.9761</v>
       </c>
       <c r="H5" t="n">
-        <v>58.2762</v>
+        <v>62.6649</v>
       </c>
     </row>
     <row r="6">
@@ -602,20 +602,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.9414</v>
+        <v>0.8232</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7804</v>
+        <v>0.0977</v>
       </c>
       <c r="G6" t="n">
-        <v>26.7918</v>
+        <v>40.842</v>
       </c>
       <c r="H6" t="n">
-        <v>57.8911</v>
+        <v>62.3852</v>
       </c>
     </row>
     <row r="7">
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9315</v>
+        <v>0.9198</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4352</v>
+        <v>0.5776</v>
       </c>
       <c r="G7" t="n">
-        <v>24.3001</v>
+        <v>26.184</v>
       </c>
       <c r="H7" t="n">
-        <v>43.2339</v>
+        <v>42.6838</v>
       </c>
     </row>
     <row r="8">
@@ -666,20 +666,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.9633</v>
+        <v>0.9704</v>
       </c>
       <c r="F8" t="n">
-        <v>1.4662</v>
+        <v>0.5178</v>
       </c>
       <c r="G8" t="n">
-        <v>18.9322</v>
+        <v>17.1824</v>
       </c>
       <c r="H8" t="n">
-        <v>44.7461</v>
+        <v>45.6074</v>
       </c>
     </row>
     <row r="9">
@@ -698,20 +698,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.9447</v>
+        <v>0.949</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3988</v>
+        <v>0.6125</v>
       </c>
       <c r="G9" t="n">
-        <v>23.1559</v>
+        <v>21.6969</v>
       </c>
       <c r="H9" t="n">
-        <v>41.3857</v>
+        <v>40.8835</v>
       </c>
     </row>
     <row r="10">
@@ -730,20 +730,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.9626</v>
+        <v>0.9708</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4678</v>
+        <v>0.5134</v>
       </c>
       <c r="G10" t="n">
-        <v>19.0434</v>
+        <v>17.0678</v>
       </c>
       <c r="H10" t="n">
-        <v>44.8206</v>
+        <v>45.812</v>
       </c>
     </row>
     <row r="11">
@@ -762,20 +762,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.9576</v>
+        <v>0.9737</v>
       </c>
       <c r="F11" t="n">
-        <v>1.4649</v>
+        <v>0.5219</v>
       </c>
       <c r="G11" t="n">
-        <v>19.9166</v>
+        <v>16.3019</v>
       </c>
       <c r="H11" t="n">
-        <v>44.6816</v>
+        <v>45.4108</v>
       </c>
     </row>
     <row r="12">
@@ -794,20 +794,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.9573</v>
+        <v>0.974</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4619</v>
+        <v>0.5258</v>
       </c>
       <c r="G12" t="n">
-        <v>19.9448</v>
+        <v>16.2883</v>
       </c>
       <c r="H12" t="n">
-        <v>44.5388</v>
+        <v>45.2282</v>
       </c>
     </row>
     <row r="13">
@@ -826,20 +826,20 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.9631</v>
+        <v>0.9727</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4472</v>
+        <v>0.5191</v>
       </c>
       <c r="G13" t="n">
-        <v>18.8356</v>
+        <v>16.7592</v>
       </c>
       <c r="H13" t="n">
-        <v>43.8248</v>
+        <v>45.5455</v>
       </c>
     </row>
     <row r="14">
@@ -858,20 +858,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9391</v>
+        <v>0.974</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4682</v>
+        <v>0.5222</v>
       </c>
       <c r="G14" t="n">
-        <v>23.4291</v>
+        <v>16.2567</v>
       </c>
       <c r="H14" t="n">
-        <v>44.842</v>
+        <v>45.3967</v>
       </c>
     </row>
     <row r="15">
@@ -890,20 +890,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9573</v>
+        <v>0.9736</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4619</v>
+        <v>0.5261</v>
       </c>
       <c r="G15" t="n">
-        <v>19.9497</v>
+        <v>16.3942</v>
       </c>
       <c r="H15" t="n">
-        <v>44.5383</v>
+        <v>45.213</v>
       </c>
     </row>
     <row r="16">
@@ -922,20 +922,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9564</v>
+        <v>0.9732</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4572</v>
+        <v>0.5193</v>
       </c>
       <c r="G16" t="n">
-        <v>20.1341</v>
+        <v>16.5129</v>
       </c>
       <c r="H16" t="n">
-        <v>44.3105</v>
+        <v>45.5346</v>
       </c>
     </row>
     <row r="17">
@@ -954,20 +954,20 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9629</v>
+        <v>0.9721</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4474</v>
+        <v>0.5201</v>
       </c>
       <c r="G17" t="n">
-        <v>18.9246</v>
+        <v>16.9388</v>
       </c>
       <c r="H17" t="n">
-        <v>43.8365</v>
+        <v>45.4993</v>
       </c>
     </row>
     <row r="18">
@@ -986,20 +986,20 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.9352</v>
+        <v>0.9705</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3984</v>
+        <v>0.5759</v>
       </c>
       <c r="G18" t="n">
-        <v>24.3446</v>
+        <v>17.0621</v>
       </c>
       <c r="H18" t="n">
-        <v>41.3663</v>
+        <v>42.771</v>
       </c>
     </row>
     <row r="19">
@@ -1018,20 +1018,20 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9340000000000001</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>1.403</v>
+        <v>0.5619</v>
       </c>
       <c r="G19" t="n">
-        <v>24.5113</v>
+        <v>21.8952</v>
       </c>
       <c r="H19" t="n">
-        <v>41.6025</v>
+        <v>43.4728</v>
       </c>
     </row>
     <row r="20">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.9215</v>
+        <v>0.9307</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4075</v>
+        <v>0.5518999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>26.665</v>
+        <v>24.6423</v>
       </c>
       <c r="H20" t="n">
-        <v>41.8334</v>
+        <v>43.964</v>
       </c>
     </row>
     <row r="21">
@@ -1082,20 +1082,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.9206</v>
+        <v>0.9301</v>
       </c>
       <c r="F21" t="n">
-        <v>1.4056</v>
+        <v>0.5643</v>
       </c>
       <c r="G21" t="n">
-        <v>26.7647</v>
+        <v>24.7486</v>
       </c>
       <c r="H21" t="n">
-        <v>41.7354</v>
+        <v>43.3498</v>
       </c>
     </row>
     <row r="22">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.9565</v>
+        <v>0.9276</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4034</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>20.5006</v>
+        <v>25.1162</v>
       </c>
       <c r="H22" t="n">
-        <v>41.6238</v>
+        <v>43.6636</v>
       </c>
     </row>
     <row r="23">
@@ -1146,20 +1146,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.9365</v>
+        <v>0.9258</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4085</v>
+        <v>0.5524</v>
       </c>
       <c r="G23" t="n">
-        <v>23.5494</v>
+        <v>25.4047</v>
       </c>
       <c r="H23" t="n">
-        <v>41.8873</v>
+        <v>43.9395</v>
       </c>
     </row>
     <row r="24">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.9302</v>
+        <v>0.9237</v>
       </c>
       <c r="F24" t="n">
-        <v>1.4088</v>
+        <v>0.5507</v>
       </c>
       <c r="G24" t="n">
-        <v>25.0567</v>
+        <v>25.7173</v>
       </c>
       <c r="H24" t="n">
-        <v>41.8984</v>
+        <v>44.0231</v>
       </c>
     </row>
     <row r="25">
@@ -1210,20 +1210,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.9192</v>
+        <v>0.9258</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4149</v>
+        <v>0.5536</v>
       </c>
       <c r="G25" t="n">
-        <v>26.9596</v>
+        <v>26.1423</v>
       </c>
       <c r="H25" t="n">
-        <v>42.2101</v>
+        <v>43.8803</v>
       </c>
     </row>
     <row r="26">
@@ -1242,20 +1242,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.95</v>
+        <v>0.953</v>
       </c>
       <c r="F26" t="n">
-        <v>1.4014</v>
+        <v>0.595</v>
       </c>
       <c r="G26" t="n">
-        <v>21.374</v>
+        <v>20.9807</v>
       </c>
       <c r="H26" t="n">
-        <v>41.5208</v>
+        <v>41.7977</v>
       </c>
     </row>
     <row r="27">
@@ -1274,20 +1274,20 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.9294</v>
+        <v>0.9357</v>
       </c>
       <c r="F27" t="n">
-        <v>1.4063</v>
+        <v>0.5742</v>
       </c>
       <c r="G27" t="n">
-        <v>25.5904</v>
+        <v>23.8894</v>
       </c>
       <c r="H27" t="n">
-        <v>41.7723</v>
+        <v>42.8561</v>
       </c>
     </row>
     <row r="28">
@@ -1310,16 +1310,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.9464</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>1.4052</v>
+        <v>0.5612</v>
       </c>
       <c r="G28" t="n">
-        <v>21.8518</v>
+        <v>23.7306</v>
       </c>
       <c r="H28" t="n">
-        <v>41.7148</v>
+        <v>43.5067</v>
       </c>
     </row>
     <row r="29">
@@ -1338,20 +1338,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.9338</v>
+        <v>0.9003</v>
       </c>
       <c r="F29" t="n">
-        <v>1.4086</v>
+        <v>0.5454</v>
       </c>
       <c r="G29" t="n">
-        <v>24.4841</v>
+        <v>29.8593</v>
       </c>
       <c r="H29" t="n">
-        <v>41.8887</v>
+        <v>44.2829</v>
       </c>
     </row>
     <row r="30">
@@ -1370,20 +1370,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.9584</v>
+        <v>0.9316</v>
       </c>
       <c r="F30" t="n">
-        <v>1.4092</v>
+        <v>0.5497</v>
       </c>
       <c r="G30" t="n">
-        <v>20.3849</v>
+        <v>24.5838</v>
       </c>
       <c r="H30" t="n">
-        <v>41.921</v>
+        <v>44.0708</v>
       </c>
     </row>
     <row r="31">
@@ -1402,20 +1402,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.9206</v>
+        <v>0.9304</v>
       </c>
       <c r="F31" t="n">
-        <v>1.403</v>
+        <v>0.5554</v>
       </c>
       <c r="G31" t="n">
-        <v>26.8066</v>
+        <v>24.7243</v>
       </c>
       <c r="H31" t="n">
-        <v>41.604</v>
+        <v>43.7903</v>
       </c>
     </row>
     <row r="32">
@@ -1434,20 +1434,20 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.9137999999999999</v>
+        <v>0.9284</v>
       </c>
       <c r="F32" t="n">
-        <v>1.4094</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>27.8922</v>
+        <v>25.0097</v>
       </c>
       <c r="H32" t="n">
-        <v>41.933</v>
+        <v>43.7679</v>
       </c>
     </row>
     <row r="33">
@@ -1466,20 +1466,20 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.9577</v>
+        <v>0.9271</v>
       </c>
       <c r="F33" t="n">
-        <v>1.4056</v>
+        <v>0.5642</v>
       </c>
       <c r="G33" t="n">
-        <v>20.3422</v>
+        <v>25.1962</v>
       </c>
       <c r="H33" t="n">
-        <v>41.736</v>
+        <v>43.3573</v>
       </c>
     </row>
     <row r="34">
@@ -1502,16 +1502,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3784</v>
+        <v>0.5996</v>
       </c>
       <c r="G34" t="n">
-        <v>16.5521</v>
+        <v>17.1242</v>
       </c>
       <c r="H34" t="n">
-        <v>40.3146</v>
+        <v>41.5588</v>
       </c>
     </row>
     <row r="35">
@@ -1530,20 +1530,20 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.9467</v>
+        <v>0.9742</v>
       </c>
       <c r="F35" t="n">
-        <v>1.3847</v>
+        <v>0.639</v>
       </c>
       <c r="G35" t="n">
-        <v>22.8522</v>
+        <v>15.9693</v>
       </c>
       <c r="H35" t="n">
-        <v>40.6447</v>
+        <v>39.4613</v>
       </c>
     </row>
     <row r="36">
@@ -1562,20 +1562,20 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.9455</v>
+        <v>0.9506</v>
       </c>
       <c r="F36" t="n">
-        <v>1.3807</v>
+        <v>0.6152</v>
       </c>
       <c r="G36" t="n">
-        <v>23.0929</v>
+        <v>21.4812</v>
       </c>
       <c r="H36" t="n">
-        <v>40.4369</v>
+        <v>40.7426</v>
       </c>
     </row>
     <row r="37">
@@ -1594,20 +1594,20 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.9473</v>
+        <v>0.9499</v>
       </c>
       <c r="F37" t="n">
-        <v>1.3715</v>
+        <v>0.615</v>
       </c>
       <c r="G37" t="n">
-        <v>22.4584</v>
+        <v>21.6926</v>
       </c>
       <c r="H37" t="n">
-        <v>39.9443</v>
+        <v>40.7507</v>
       </c>
     </row>
     <row r="38">
@@ -1630,16 +1630,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.9435</v>
+        <v>0.9382</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3746</v>
+        <v>0.6155</v>
       </c>
       <c r="G38" t="n">
-        <v>23.0092</v>
+        <v>24.0988</v>
       </c>
       <c r="H38" t="n">
-        <v>40.1105</v>
+        <v>40.7274</v>
       </c>
     </row>
     <row r="39">
@@ -1658,20 +1658,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.9432</v>
+        <v>0.9481000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3769</v>
+        <v>0.6202</v>
       </c>
       <c r="G39" t="n">
-        <v>22.7951</v>
+        <v>21.8029</v>
       </c>
       <c r="H39" t="n">
-        <v>40.2315</v>
+        <v>40.4769</v>
       </c>
     </row>
     <row r="40">
@@ -1690,20 +1690,20 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.945</v>
+        <v>0.9363</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3783</v>
+        <v>0.6242</v>
       </c>
       <c r="G40" t="n">
-        <v>22.6186</v>
+        <v>24.2167</v>
       </c>
       <c r="H40" t="n">
-        <v>40.309</v>
+        <v>40.2624</v>
       </c>
     </row>
     <row r="41">
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.9726</v>
+        <v>0.97</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3799</v>
+        <v>0.602</v>
       </c>
       <c r="G41" t="n">
-        <v>16.4738</v>
+        <v>17.1074</v>
       </c>
       <c r="H41" t="n">
-        <v>40.3897</v>
+        <v>41.4347</v>
       </c>
     </row>
     <row r="42">
@@ -1754,20 +1754,20 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.9466</v>
+        <v>0.9739</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3879</v>
+        <v>0.6317</v>
       </c>
       <c r="G42" t="n">
-        <v>22.8696</v>
+        <v>16.0704</v>
       </c>
       <c r="H42" t="n">
-        <v>40.8133</v>
+        <v>39.8589</v>
       </c>
     </row>
     <row r="43">
@@ -1786,20 +1786,20 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.9447</v>
+        <v>0.9507</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3849</v>
+        <v>0.6146</v>
       </c>
       <c r="G43" t="n">
-        <v>23.2662</v>
+        <v>21.4505</v>
       </c>
       <c r="H43" t="n">
-        <v>40.6573</v>
+        <v>40.7744</v>
       </c>
     </row>
     <row r="44">
@@ -1818,20 +1818,20 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.9475</v>
+        <v>0.95</v>
       </c>
       <c r="F44" t="n">
-        <v>1.3724</v>
+        <v>0.6161</v>
       </c>
       <c r="G44" t="n">
-        <v>22.4681</v>
+        <v>21.6903</v>
       </c>
       <c r="H44" t="n">
-        <v>39.9893</v>
+        <v>40.6946</v>
       </c>
     </row>
     <row r="45">
@@ -1854,16 +1854,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.9446</v>
+        <v>0.9396</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3627</v>
+        <v>0.6166</v>
       </c>
       <c r="G45" t="n">
-        <v>22.9149</v>
+        <v>23.8527</v>
       </c>
       <c r="H45" t="n">
-        <v>39.4668</v>
+        <v>40.6654</v>
       </c>
     </row>
     <row r="46">
@@ -1882,20 +1882,20 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.9444</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>1.3791</v>
+        <v>0.6226</v>
       </c>
       <c r="G46" t="n">
-        <v>22.6427</v>
+        <v>23.6619</v>
       </c>
       <c r="H46" t="n">
-        <v>40.3507</v>
+        <v>40.3491</v>
       </c>
     </row>
     <row r="47">
@@ -1914,20 +1914,20 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.9449</v>
+        <v>0.9367</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3852</v>
+        <v>0.6274999999999999</v>
       </c>
       <c r="G47" t="n">
-        <v>22.6568</v>
+        <v>24.1367</v>
       </c>
       <c r="H47" t="n">
-        <v>40.673</v>
+        <v>40.0821</v>
       </c>
     </row>
     <row r="48">
@@ -1946,20 +1946,20 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.9432</v>
+        <v>0.9494</v>
       </c>
       <c r="F48" t="n">
-        <v>1.3936</v>
+        <v>0.6201</v>
       </c>
       <c r="G48" t="n">
-        <v>23.0784</v>
+        <v>21.7255</v>
       </c>
       <c r="H48" t="n">
-        <v>41.115</v>
+        <v>40.481</v>
       </c>
     </row>
     <row r="49">
@@ -1978,20 +1978,20 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.953</v>
+        <v>0.9495</v>
       </c>
       <c r="F49" t="n">
-        <v>1.38</v>
+        <v>0.6193</v>
       </c>
       <c r="G49" t="n">
-        <v>20.8611</v>
+        <v>21.5737</v>
       </c>
       <c r="H49" t="n">
-        <v>40.3967</v>
+        <v>40.5257</v>
       </c>
     </row>
     <row r="50">
@@ -2010,20 +2010,20 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.8914</v>
+        <v>0.9689</v>
       </c>
       <c r="F50" t="n">
-        <v>1.775</v>
+        <v>0.1721</v>
       </c>
       <c r="G50" t="n">
-        <v>34.8317</v>
+        <v>21.7795</v>
       </c>
       <c r="H50" t="n">
-        <v>57.6922</v>
+        <v>59.758</v>
       </c>
     </row>
     <row r="51">
@@ -2046,16 +2046,16 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8639</v>
+        <v>0.85</v>
       </c>
       <c r="F51" t="n">
-        <v>1.7649</v>
+        <v>0.1757</v>
       </c>
       <c r="G51" t="n">
-        <v>37.6518</v>
+        <v>39.0306</v>
       </c>
       <c r="H51" t="n">
-        <v>57.3137</v>
+        <v>59.6288</v>
       </c>
     </row>
     <row r="52">
@@ -2074,20 +2074,20 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.8369</v>
+        <v>0.8446</v>
       </c>
       <c r="F52" t="n">
-        <v>1.7591</v>
+        <v>0.1695</v>
       </c>
       <c r="G52" t="n">
-        <v>39.7738</v>
+        <v>39.2564</v>
       </c>
       <c r="H52" t="n">
-        <v>57.0967</v>
+        <v>59.8514</v>
       </c>
     </row>
     <row r="53">
@@ -2106,20 +2106,20 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.8793</v>
       </c>
       <c r="F53" t="n">
-        <v>1.7486</v>
+        <v>0.222</v>
       </c>
       <c r="G53" t="n">
-        <v>37.5511</v>
+        <v>36.6544</v>
       </c>
       <c r="H53" t="n">
-        <v>56.7012</v>
+        <v>57.9315</v>
       </c>
     </row>
     <row r="54">
@@ -2138,20 +2138,20 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.8713</v>
+        <v>0.9732</v>
       </c>
       <c r="F54" t="n">
-        <v>1.7255</v>
+        <v>0.2572</v>
       </c>
       <c r="G54" t="n">
-        <v>36.5813</v>
+        <v>20.4079</v>
       </c>
       <c r="H54" t="n">
-        <v>55.8172</v>
+        <v>56.6047</v>
       </c>
     </row>
     <row r="55">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8538</v>
+        <v>0.8363</v>
       </c>
       <c r="F55" t="n">
-        <v>1.7721</v>
+        <v>0.1378</v>
       </c>
       <c r="G55" t="n">
-        <v>37.992</v>
+        <v>39.9942</v>
       </c>
       <c r="H55" t="n">
-        <v>57.5836</v>
+        <v>60.9838</v>
       </c>
     </row>
     <row r="56">
@@ -2202,20 +2202,20 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8615</v>
+        <v>0.8832</v>
       </c>
       <c r="F56" t="n">
-        <v>1.7577</v>
+        <v>0.1586</v>
       </c>
       <c r="G56" t="n">
-        <v>37.9013</v>
+        <v>35.6331</v>
       </c>
       <c r="H56" t="n">
-        <v>57.0436</v>
+        <v>60.2429</v>
       </c>
     </row>
     <row r="57">
@@ -2234,20 +2234,20 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.864</v>
+        <v>0.8754</v>
       </c>
       <c r="F57" t="n">
-        <v>1.7466</v>
+        <v>0.1769</v>
       </c>
       <c r="G57" t="n">
-        <v>37.631</v>
+        <v>36.7643</v>
       </c>
       <c r="H57" t="n">
-        <v>56.6254</v>
+        <v>59.5856</v>
       </c>
     </row>
     <row r="58">
@@ -2266,20 +2266,20 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9408</v>
+        <v>0.8234</v>
       </c>
       <c r="F58" t="n">
-        <v>1.7802</v>
+        <v>0.1013</v>
       </c>
       <c r="G58" t="n">
-        <v>26.9446</v>
+        <v>40.7634</v>
       </c>
       <c r="H58" t="n">
-        <v>57.8834</v>
+        <v>62.2623</v>
       </c>
     </row>
     <row r="59">
@@ -2298,20 +2298,20 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.9358</v>
+        <v>0.8244</v>
       </c>
       <c r="F59" t="n">
-        <v>1.7798</v>
+        <v>0.102</v>
       </c>
       <c r="G59" t="n">
-        <v>27.1568</v>
+        <v>40.7814</v>
       </c>
       <c r="H59" t="n">
-        <v>57.8704</v>
+        <v>62.2383</v>
       </c>
     </row>
     <row r="60">
@@ -2330,20 +2330,20 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9365</v>
+        <v>0.8246</v>
       </c>
       <c r="F60" t="n">
-        <v>1.78</v>
+        <v>0.1033</v>
       </c>
       <c r="G60" t="n">
-        <v>27.0186</v>
+        <v>40.7737</v>
       </c>
       <c r="H60" t="n">
-        <v>57.876</v>
+        <v>62.1909</v>
       </c>
     </row>
     <row r="61">
@@ -2362,20 +2362,20 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.9396</v>
+        <v>0.8244</v>
       </c>
       <c r="F61" t="n">
-        <v>1.778</v>
+        <v>0.1061</v>
       </c>
       <c r="G61" t="n">
-        <v>27.0022</v>
+        <v>40.7399</v>
       </c>
       <c r="H61" t="n">
-        <v>57.8034</v>
+        <v>62.0943</v>
       </c>
     </row>
     <row r="62">
@@ -2398,16 +2398,16 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.8415</v>
+        <v>0.8299</v>
       </c>
       <c r="F62" t="n">
-        <v>1.7884</v>
+        <v>0.1227</v>
       </c>
       <c r="G62" t="n">
-        <v>38.5502</v>
+        <v>40.0818</v>
       </c>
       <c r="H62" t="n">
-        <v>58.1883</v>
+        <v>61.5152</v>
       </c>
     </row>
     <row r="63">
@@ -2426,20 +2426,20 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.8608</v>
+        <v>0.8537</v>
       </c>
       <c r="F63" t="n">
-        <v>1.7881</v>
+        <v>0.116</v>
       </c>
       <c r="G63" t="n">
-        <v>36.5895</v>
+        <v>37.9973</v>
       </c>
       <c r="H63" t="n">
-        <v>58.1783</v>
+        <v>61.7511</v>
       </c>
     </row>
     <row r="64">
@@ -2458,20 +2458,20 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.8692</v>
+        <v>0.8537</v>
       </c>
       <c r="F64" t="n">
-        <v>1.7872</v>
+        <v>0.1248</v>
       </c>
       <c r="G64" t="n">
-        <v>36.1385</v>
+        <v>37.8335</v>
       </c>
       <c r="H64" t="n">
-        <v>58.1433</v>
+        <v>61.4439</v>
       </c>
     </row>
     <row r="65">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.8613</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="F65" t="n">
-        <v>1.7847</v>
+        <v>0.1231</v>
       </c>
       <c r="G65" t="n">
-        <v>36.7981</v>
+        <v>40.2301</v>
       </c>
       <c r="H65" t="n">
-        <v>58.0509</v>
+        <v>61.5023</v>
       </c>
     </row>
     <row r="66">
@@ -2522,20 +2522,20 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.8915</v>
+        <v>0.8491</v>
       </c>
       <c r="F66" t="n">
-        <v>1.7477</v>
+        <v>0.1783</v>
       </c>
       <c r="G66" t="n">
-        <v>34.3183</v>
+        <v>39.1537</v>
       </c>
       <c r="H66" t="n">
-        <v>56.6655</v>
+        <v>59.5364</v>
       </c>
     </row>
     <row r="67">
@@ -2554,20 +2554,20 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.8774</v>
+        <v>0.8474</v>
       </c>
       <c r="F67" t="n">
-        <v>1.7556</v>
+        <v>0.1541</v>
       </c>
       <c r="G67" t="n">
-        <v>36.1072</v>
+        <v>39.4465</v>
       </c>
       <c r="H67" t="n">
-        <v>56.9639</v>
+        <v>60.4067</v>
       </c>
     </row>
     <row r="68">
@@ -2586,20 +2586,20 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.9131</v>
+        <v>0.8663999999999999</v>
       </c>
       <c r="F68" t="n">
-        <v>1.7523</v>
+        <v>0.1625</v>
       </c>
       <c r="G68" t="n">
-        <v>31.0511</v>
+        <v>37.6349</v>
       </c>
       <c r="H68" t="n">
-        <v>56.8406</v>
+        <v>60.1045</v>
       </c>
     </row>
     <row r="69">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.9555</v>
+        <v>0.9635</v>
       </c>
       <c r="F69" t="n">
-        <v>1.4308</v>
+        <v>0.5532</v>
       </c>
       <c r="G69" t="n">
-        <v>20.6827</v>
+        <v>18.8451</v>
       </c>
       <c r="H69" t="n">
-        <v>43.0133</v>
+        <v>43.9003</v>
       </c>
     </row>
     <row r="70">
@@ -2650,20 +2650,20 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.9311</v>
+        <v>0.9616</v>
       </c>
       <c r="F70" t="n">
-        <v>1.4264</v>
+        <v>0.5612</v>
       </c>
       <c r="G70" t="n">
-        <v>24.8029</v>
+        <v>19.0594</v>
       </c>
       <c r="H70" t="n">
-        <v>42.7936</v>
+        <v>43.5063</v>
       </c>
     </row>
     <row r="71">
@@ -2682,20 +2682,20 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.9752999999999999</v>
+        <v>0.9486</v>
       </c>
       <c r="F71" t="n">
-        <v>1.4327</v>
+        <v>0.5687</v>
       </c>
       <c r="G71" t="n">
-        <v>15.3741</v>
+        <v>21.8805</v>
       </c>
       <c r="H71" t="n">
-        <v>43.1087</v>
+        <v>43.1337</v>
       </c>
     </row>
     <row r="72">
@@ -2714,20 +2714,20 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.9498</v>
+        <v>0.9307</v>
       </c>
       <c r="F72" t="n">
-        <v>1.4335</v>
+        <v>0.5508</v>
       </c>
       <c r="G72" t="n">
-        <v>21.3599</v>
+        <v>24.7105</v>
       </c>
       <c r="H72" t="n">
-        <v>43.1493</v>
+        <v>44.0204</v>
       </c>
     </row>
     <row r="73">
@@ -2746,20 +2746,20 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.9673</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="F73" t="n">
-        <v>1.445</v>
+        <v>0.5517</v>
       </c>
       <c r="G73" t="n">
-        <v>18.6537</v>
+        <v>24.0906</v>
       </c>
       <c r="H73" t="n">
-        <v>43.7181</v>
+        <v>43.9752</v>
       </c>
     </row>
     <row r="74">
@@ -2778,20 +2778,20 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.9366</v>
+        <v>0.9757</v>
       </c>
       <c r="F74" t="n">
-        <v>1.442</v>
+        <v>0.5467</v>
       </c>
       <c r="G74" t="n">
-        <v>24.5659</v>
+        <v>16.5047</v>
       </c>
       <c r="H74" t="n">
-        <v>43.5693</v>
+        <v>44.22</v>
       </c>
     </row>
     <row r="75">
@@ -2810,20 +2810,20 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.9305</v>
+        <v>0.8961</v>
       </c>
       <c r="F75" t="n">
-        <v>1.4567</v>
+        <v>0.4991</v>
       </c>
       <c r="G75" t="n">
-        <v>24.7148</v>
+        <v>29.7767</v>
       </c>
       <c r="H75" t="n">
-        <v>44.2871</v>
+        <v>46.482</v>
       </c>
     </row>
     <row r="76">
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.9305</v>
+        <v>0.8961</v>
       </c>
       <c r="F76" t="n">
-        <v>1.4567</v>
+        <v>0.4991</v>
       </c>
       <c r="G76" t="n">
-        <v>24.7148</v>
+        <v>29.7767</v>
       </c>
       <c r="H76" t="n">
-        <v>44.2871</v>
+        <v>46.482</v>
       </c>
     </row>
     <row r="77">
@@ -2874,20 +2874,20 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.8699</v>
+        <v>0.8222</v>
       </c>
       <c r="F77" t="n">
-        <v>1.7726</v>
+        <v>0.1332</v>
       </c>
       <c r="G77" t="n">
-        <v>36.0165</v>
+        <v>40.6307</v>
       </c>
       <c r="H77" t="n">
-        <v>57.6014</v>
+        <v>61.1474</v>
       </c>
     </row>
     <row r="78">
@@ -2906,20 +2906,20 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.8809</v>
+        <v>0.8233</v>
       </c>
       <c r="F78" t="n">
-        <v>1.7687</v>
+        <v>0.1379</v>
       </c>
       <c r="G78" t="n">
-        <v>34.2671</v>
+        <v>40.5138</v>
       </c>
       <c r="H78" t="n">
-        <v>57.4587</v>
+        <v>60.9824</v>
       </c>
     </row>
     <row r="79">
@@ -2938,20 +2938,20 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.9379999999999999</v>
+        <v>0.8237</v>
       </c>
       <c r="F79" t="n">
-        <v>1.7691</v>
+        <v>0.1342</v>
       </c>
       <c r="G79" t="n">
-        <v>26.6891</v>
+        <v>40.4898</v>
       </c>
       <c r="H79" t="n">
-        <v>57.4727</v>
+        <v>61.1104</v>
       </c>
     </row>
     <row r="80">
@@ -2970,20 +2970,20 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.8809</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="F80" t="n">
-        <v>1.7684</v>
+        <v>0.1375</v>
       </c>
       <c r="G80" t="n">
-        <v>34.2684</v>
+        <v>40.5283</v>
       </c>
       <c r="H80" t="n">
-        <v>57.4455</v>
+        <v>60.9941</v>
       </c>
     </row>
     <row r="81">
@@ -3006,16 +3006,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.8505</v>
+        <v>0.8364</v>
       </c>
       <c r="F81" t="n">
-        <v>1.7478</v>
+        <v>0.1222</v>
       </c>
       <c r="G81" t="n">
-        <v>38.0116</v>
+        <v>39.6382</v>
       </c>
       <c r="H81" t="n">
-        <v>56.6721</v>
+        <v>61.5335</v>
       </c>
     </row>
     <row r="82">
@@ -3038,16 +3038,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.8473000000000001</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="F82" t="n">
-        <v>1.7568</v>
+        <v>0.1223</v>
       </c>
       <c r="G82" t="n">
-        <v>38.2528</v>
+        <v>39.4464</v>
       </c>
       <c r="H82" t="n">
-        <v>57.0092</v>
+        <v>61.5307</v>
       </c>
     </row>
     <row r="83">
@@ -3066,20 +3066,20 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.93</v>
+        <v>0.8953</v>
       </c>
       <c r="F83" t="n">
-        <v>1.4543</v>
+        <v>0.5026</v>
       </c>
       <c r="G83" t="n">
-        <v>24.7672</v>
+        <v>29.8384</v>
       </c>
       <c r="H83" t="n">
-        <v>44.1722</v>
+        <v>46.3192</v>
       </c>
     </row>
     <row r="84">
@@ -3098,20 +3098,20 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.9308</v>
+        <v>0.8956</v>
       </c>
       <c r="F84" t="n">
-        <v>1.4548</v>
+        <v>0.5034999999999999</v>
       </c>
       <c r="G84" t="n">
-        <v>24.6533</v>
+        <v>29.8015</v>
       </c>
       <c r="H84" t="n">
-        <v>44.1975</v>
+        <v>46.2773</v>
       </c>
     </row>
     <row r="85">
@@ -3130,20 +3130,20 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.9301</v>
+        <v>0.8954</v>
       </c>
       <c r="F85" t="n">
-        <v>1.4548</v>
+        <v>0.5004</v>
       </c>
       <c r="G85" t="n">
-        <v>24.7593</v>
+        <v>29.8362</v>
       </c>
       <c r="H85" t="n">
-        <v>44.1949</v>
+        <v>46.4213</v>
       </c>
     </row>
     <row r="86">
@@ -3162,20 +3162,20 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.964</v>
+        <v>0.9419</v>
       </c>
       <c r="F86" t="n">
-        <v>1.3958</v>
+        <v>0.5894</v>
       </c>
       <c r="G86" t="n">
-        <v>18.7919</v>
+        <v>22.9091</v>
       </c>
       <c r="H86" t="n">
-        <v>41.2281</v>
+        <v>42.0841</v>
       </c>
     </row>
     <row r="87">
@@ -3194,20 +3194,20 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.95</v>
+        <v>0.9497</v>
       </c>
       <c r="F87" t="n">
-        <v>1.4</v>
+        <v>0.5652</v>
       </c>
       <c r="G87" t="n">
-        <v>21.3739</v>
+        <v>21.5811</v>
       </c>
       <c r="H87" t="n">
-        <v>41.4478</v>
+        <v>43.3063</v>
       </c>
     </row>
     <row r="88">
@@ -3226,20 +3226,20 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.9537</v>
+        <v>0.9542</v>
       </c>
       <c r="F88" t="n">
-        <v>1.4098</v>
+        <v>0.5635</v>
       </c>
       <c r="G88" t="n">
-        <v>21.0797</v>
+        <v>20.8089</v>
       </c>
       <c r="H88" t="n">
-        <v>41.9511</v>
+        <v>43.3906</v>
       </c>
     </row>
     <row r="89">
@@ -3258,20 +3258,20 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.9351</v>
+        <v>0.9641999999999999</v>
       </c>
       <c r="F89" t="n">
-        <v>1.4073</v>
+        <v>0.5626</v>
       </c>
       <c r="G89" t="n">
-        <v>24.4372</v>
+        <v>19.2314</v>
       </c>
       <c r="H89" t="n">
-        <v>41.8251</v>
+        <v>43.4363</v>
       </c>
     </row>
     <row r="90">
@@ -3290,20 +3290,20 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.9447</v>
+        <v>0.9507</v>
       </c>
       <c r="F90" t="n">
-        <v>1.3846</v>
+        <v>0.6145</v>
       </c>
       <c r="G90" t="n">
-        <v>23.2666</v>
+        <v>21.4505</v>
       </c>
       <c r="H90" t="n">
-        <v>40.6393</v>
+        <v>40.7765</v>
       </c>
     </row>
     <row r="91">
@@ -3322,20 +3322,20 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.9475</v>
+        <v>0.95</v>
       </c>
       <c r="F91" t="n">
-        <v>1.3723</v>
+        <v>0.6161</v>
       </c>
       <c r="G91" t="n">
-        <v>22.4672</v>
+        <v>21.6903</v>
       </c>
       <c r="H91" t="n">
-        <v>39.9884</v>
+        <v>40.6931</v>
       </c>
     </row>
     <row r="92">
@@ -3354,20 +3354,20 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.9537</v>
+        <v>0.9542</v>
       </c>
       <c r="F92" t="n">
-        <v>1.4098</v>
+        <v>0.5635</v>
       </c>
       <c r="G92" t="n">
-        <v>21.0797</v>
+        <v>20.8089</v>
       </c>
       <c r="H92" t="n">
-        <v>41.9511</v>
+        <v>43.3906</v>
       </c>
     </row>
     <row r="93">
@@ -3386,20 +3386,20 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.9475</v>
+        <v>0.95</v>
       </c>
       <c r="F93" t="n">
-        <v>1.3723</v>
+        <v>0.6161</v>
       </c>
       <c r="G93" t="n">
-        <v>22.4672</v>
+        <v>21.6903</v>
       </c>
       <c r="H93" t="n">
-        <v>39.9884</v>
+        <v>40.6931</v>
       </c>
     </row>
     <row r="94">
@@ -3422,16 +3422,16 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.9265</v>
+        <v>0.9169</v>
       </c>
       <c r="F94" t="n">
-        <v>1.4451</v>
+        <v>0.503</v>
       </c>
       <c r="G94" t="n">
-        <v>25.6773</v>
+        <v>27.2423</v>
       </c>
       <c r="H94" t="n">
-        <v>43.7205</v>
+        <v>46.2989</v>
       </c>
     </row>
     <row r="95">
@@ -3450,20 +3450,20 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.7848000000000001</v>
+        <v>0.8089</v>
       </c>
       <c r="F95" t="n">
-        <v>2.0905</v>
+        <v>-0.0878</v>
       </c>
       <c r="G95" t="n">
-        <v>47.1317</v>
+        <v>43.4651</v>
       </c>
       <c r="H95" t="n">
-        <v>68.43519999999999</v>
+        <v>68.4996</v>
       </c>
     </row>
     <row r="96">
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.9268999999999999</v>
+        <v>0.9165</v>
       </c>
       <c r="F96" t="n">
-        <v>1.442</v>
+        <v>0.505</v>
       </c>
       <c r="G96" t="n">
-        <v>25.5813</v>
+        <v>27.2851</v>
       </c>
       <c r="H96" t="n">
-        <v>43.5663</v>
+        <v>46.2087</v>
       </c>
     </row>
     <row r="97">
@@ -3518,16 +3518,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.9265</v>
+        <v>0.9164</v>
       </c>
       <c r="F97" t="n">
-        <v>1.4427</v>
+        <v>0.5031</v>
       </c>
       <c r="G97" t="n">
-        <v>25.6296</v>
+        <v>27.3283</v>
       </c>
       <c r="H97" t="n">
-        <v>43.6045</v>
+        <v>46.2948</v>
       </c>
     </row>
     <row r="98">
@@ -3546,20 +3546,20 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.9474</v>
+        <v>0.9615</v>
       </c>
       <c r="F98" t="n">
-        <v>1.3771</v>
+        <v>0.5919</v>
       </c>
       <c r="G98" t="n">
-        <v>22.5343</v>
+        <v>20.2279</v>
       </c>
       <c r="H98" t="n">
-        <v>40.2419</v>
+        <v>41.9584</v>
       </c>
     </row>
     <row r="99">
@@ -3578,20 +3578,20 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.9635</v>
+        <v>0.9222</v>
       </c>
       <c r="F99" t="n">
-        <v>1.3797</v>
+        <v>0.5854</v>
       </c>
       <c r="G99" t="n">
-        <v>19.3477</v>
+        <v>26.8129</v>
       </c>
       <c r="H99" t="n">
-        <v>40.3837</v>
+        <v>42.2868</v>
       </c>
     </row>
     <row r="100">
@@ -3610,20 +3610,20 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.9314</v>
+        <v>0.9191</v>
       </c>
       <c r="F100" t="n">
-        <v>1.3793</v>
+        <v>0.5764</v>
       </c>
       <c r="G100" t="n">
-        <v>25.3157</v>
+        <v>27.2166</v>
       </c>
       <c r="H100" t="n">
-        <v>40.3612</v>
+        <v>42.7451</v>
       </c>
     </row>
     <row r="101">
@@ -3642,20 +3642,20 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.9618</v>
+        <v>0.9167</v>
       </c>
       <c r="F101" t="n">
-        <v>1.3781</v>
+        <v>0.5885</v>
       </c>
       <c r="G101" t="n">
-        <v>19.6167</v>
+        <v>27.4852</v>
       </c>
       <c r="H101" t="n">
-        <v>40.2966</v>
+        <v>42.132</v>
       </c>
     </row>
     <row r="102">
@@ -3674,20 +3674,20 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.9176</v>
       </c>
       <c r="F102" t="n">
-        <v>1.3807</v>
+        <v>0.5868</v>
       </c>
       <c r="G102" t="n">
-        <v>23.631</v>
+        <v>27.5001</v>
       </c>
       <c r="H102" t="n">
-        <v>40.4327</v>
+        <v>42.2152</v>
       </c>
     </row>
     <row r="103">
@@ -3706,20 +3706,20 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.9757</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="F103" t="n">
-        <v>1.3698</v>
+        <v>0.6051</v>
       </c>
       <c r="G103" t="n">
-        <v>16.1569</v>
+        <v>17.3473</v>
       </c>
       <c r="H103" t="n">
-        <v>39.8523</v>
+        <v>41.2716</v>
       </c>
     </row>
     <row r="104">
@@ -3742,16 +3742,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.9372</v>
+        <v>0.9248</v>
       </c>
       <c r="F104" t="n">
-        <v>1.389</v>
+        <v>0.5821</v>
       </c>
       <c r="G104" t="n">
-        <v>24.6145</v>
+        <v>26.5311</v>
       </c>
       <c r="H104" t="n">
-        <v>40.8747</v>
+        <v>42.4578</v>
       </c>
     </row>
     <row r="105">
@@ -3770,20 +3770,20 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.9666</v>
+        <v>0.9225</v>
       </c>
       <c r="F105" t="n">
-        <v>1.3877</v>
+        <v>0.5899</v>
       </c>
       <c r="G105" t="n">
-        <v>18.7989</v>
+        <v>26.7699</v>
       </c>
       <c r="H105" t="n">
-        <v>40.8068</v>
+        <v>42.0576</v>
       </c>
     </row>
     <row r="106">
@@ -3806,16 +3806,16 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.9342</v>
+        <v>0.9221</v>
       </c>
       <c r="F106" t="n">
-        <v>1.3808</v>
+        <v>0.5756</v>
       </c>
       <c r="G106" t="n">
-        <v>25.0083</v>
+        <v>26.9178</v>
       </c>
       <c r="H106" t="n">
-        <v>40.4422</v>
+        <v>42.7853</v>
       </c>
     </row>
     <row r="107">
@@ -3834,20 +3834,20 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.9772</v>
+        <v>0.9192</v>
       </c>
       <c r="F107" t="n">
-        <v>1.3806</v>
+        <v>0.5794</v>
       </c>
       <c r="G107" t="n">
-        <v>15.4265</v>
+        <v>27.1478</v>
       </c>
       <c r="H107" t="n">
-        <v>40.4295</v>
+        <v>42.5957</v>
       </c>
     </row>
     <row r="108">
@@ -3870,16 +3870,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.9349</v>
+        <v>0.9285</v>
       </c>
       <c r="F108" t="n">
-        <v>1.4547</v>
+        <v>0.5314</v>
       </c>
       <c r="G108" t="n">
-        <v>25.4454</v>
+        <v>26.3822</v>
       </c>
       <c r="H108" t="n">
-        <v>44.1909</v>
+        <v>44.9573</v>
       </c>
     </row>
     <row r="109">
@@ -3898,20 +3898,20 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.9381</v>
+        <v>0.9754</v>
       </c>
       <c r="F109" t="n">
-        <v>1.4471</v>
+        <v>0.5451</v>
       </c>
       <c r="G109" t="n">
-        <v>24.783</v>
+        <v>16.6001</v>
       </c>
       <c r="H109" t="n">
-        <v>43.8199</v>
+        <v>44.2955</v>
       </c>
     </row>
     <row r="110">
@@ -3930,20 +3930,20 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.9811</v>
+        <v>0.945</v>
       </c>
       <c r="F110" t="n">
-        <v>1.4432</v>
+        <v>0.5443</v>
       </c>
       <c r="G110" t="n">
-        <v>15.1634</v>
+        <v>23.5377</v>
       </c>
       <c r="H110" t="n">
-        <v>43.6275</v>
+        <v>44.3376</v>
       </c>
     </row>
     <row r="111">
@@ -3962,20 +3962,20 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.9821</v>
+        <v>0.9762</v>
       </c>
       <c r="F111" t="n">
-        <v>1.4185</v>
+        <v>0.5573</v>
       </c>
       <c r="G111" t="n">
-        <v>14.5135</v>
+        <v>16.2484</v>
       </c>
       <c r="H111" t="n">
-        <v>42.3931</v>
+        <v>43.697</v>
       </c>
     </row>
     <row r="112">
@@ -3994,20 +3994,20 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.9362</v>
+        <v>0.9284</v>
       </c>
       <c r="F112" t="n">
-        <v>1.4547</v>
+        <v>0.5311</v>
       </c>
       <c r="G112" t="n">
-        <v>25.222</v>
+        <v>26.4107</v>
       </c>
       <c r="H112" t="n">
-        <v>44.1881</v>
+        <v>44.975</v>
       </c>
     </row>
     <row r="113">
@@ -4026,20 +4026,20 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.9385</v>
+        <v>0.9476</v>
       </c>
       <c r="F113" t="n">
-        <v>1.4481</v>
+        <v>0.5477</v>
       </c>
       <c r="G113" t="n">
-        <v>24.7706</v>
+        <v>23.1087</v>
       </c>
       <c r="H113" t="n">
-        <v>43.8706</v>
+        <v>44.1692</v>
       </c>
     </row>
     <row r="114">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.9811</v>
+        <v>0.945</v>
       </c>
       <c r="F114" t="n">
-        <v>1.4426</v>
+        <v>0.548</v>
       </c>
       <c r="G114" t="n">
-        <v>15.1581</v>
+        <v>23.4792</v>
       </c>
       <c r="H114" t="n">
-        <v>43.6001</v>
+        <v>44.1545</v>
       </c>
     </row>
     <row r="115">
@@ -4090,20 +4090,20 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.9817</v>
+        <v>0.9749</v>
       </c>
       <c r="F115" t="n">
-        <v>1.4215</v>
+        <v>0.5591</v>
       </c>
       <c r="G115" t="n">
-        <v>14.6775</v>
+        <v>16.1972</v>
       </c>
       <c r="H115" t="n">
-        <v>42.5479</v>
+        <v>43.608</v>
       </c>
     </row>
     <row r="116">
@@ -4126,16 +4126,16 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.8248</v>
+        <v>0.8028</v>
       </c>
       <c r="F116" t="n">
-        <v>1.7971</v>
+        <v>0.1232</v>
       </c>
       <c r="G116" t="n">
-        <v>40.6032</v>
+        <v>42.9803</v>
       </c>
       <c r="H116" t="n">
-        <v>58.5079</v>
+        <v>61.4974</v>
       </c>
     </row>
     <row r="117">
@@ -4154,20 +4154,20 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.8242</v>
+        <v>0.8229</v>
       </c>
       <c r="F117" t="n">
-        <v>1.7932</v>
+        <v>0.1245</v>
       </c>
       <c r="G117" t="n">
-        <v>40.6691</v>
+        <v>41.3447</v>
       </c>
       <c r="H117" t="n">
-        <v>58.3656</v>
+        <v>61.4543</v>
       </c>
     </row>
     <row r="118">
@@ -4186,20 +4186,20 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.9666</v>
+        <v>0.9225</v>
       </c>
       <c r="F118" t="n">
-        <v>1.3877</v>
+        <v>0.5899</v>
       </c>
       <c r="G118" t="n">
-        <v>18.7989</v>
+        <v>26.7699</v>
       </c>
       <c r="H118" t="n">
-        <v>40.8068</v>
+        <v>42.0576</v>
       </c>
     </row>
     <row r="119">
@@ -4218,20 +4218,20 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.9385</v>
+        <v>0.9476</v>
       </c>
       <c r="F119" t="n">
-        <v>1.4481</v>
+        <v>0.5477</v>
       </c>
       <c r="G119" t="n">
-        <v>24.7706</v>
+        <v>23.1087</v>
       </c>
       <c r="H119" t="n">
-        <v>43.8706</v>
+        <v>44.1692</v>
       </c>
     </row>
     <row r="120">
@@ -4250,20 +4250,20 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.9332</v>
+        <v>0.8863</v>
       </c>
       <c r="F120" t="n">
-        <v>1.5021</v>
+        <v>0.4742</v>
       </c>
       <c r="G120" t="n">
-        <v>24.5573</v>
+        <v>31.4256</v>
       </c>
       <c r="H120" t="n">
-        <v>46.4371</v>
+        <v>47.6258</v>
       </c>
     </row>
     <row r="121">
@@ -4282,20 +4282,20 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.9332</v>
+        <v>0.8863</v>
       </c>
       <c r="F121" t="n">
-        <v>1.5021</v>
+        <v>0.4742</v>
       </c>
       <c r="G121" t="n">
-        <v>24.5573</v>
+        <v>31.4256</v>
       </c>
       <c r="H121" t="n">
-        <v>46.4371</v>
+        <v>47.6258</v>
       </c>
     </row>
     <row r="122">
@@ -4314,20 +4314,20 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.9327</v>
+        <v>0.931</v>
       </c>
       <c r="F122" t="n">
-        <v>1.4002</v>
+        <v>0.6031</v>
       </c>
       <c r="G122" t="n">
-        <v>24.2758</v>
+        <v>24.641</v>
       </c>
       <c r="H122" t="n">
-        <v>41.4573</v>
+        <v>41.3771</v>
       </c>
     </row>
     <row r="123">
@@ -4346,20 +4346,20 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.9384</v>
+        <v>0.9767</v>
       </c>
       <c r="F123" t="n">
-        <v>1.4484</v>
+        <v>0.5488</v>
       </c>
       <c r="G123" t="n">
-        <v>24.7904</v>
+        <v>16.4153</v>
       </c>
       <c r="H123" t="n">
-        <v>43.8808</v>
+        <v>44.1153</v>
       </c>
     </row>
     <row r="124">
@@ -4378,20 +4378,20 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.9804</v>
+        <v>0.9613</v>
       </c>
       <c r="F124" t="n">
-        <v>1.4454</v>
+        <v>0.5561</v>
       </c>
       <c r="G124" t="n">
-        <v>16.0758</v>
+        <v>20.3816</v>
       </c>
       <c r="H124" t="n">
-        <v>43.7372</v>
+        <v>43.7586</v>
       </c>
     </row>
     <row r="125">
@@ -4410,20 +4410,20 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.9766</v>
+        <v>0.9164</v>
       </c>
       <c r="F125" t="n">
-        <v>1.4439</v>
+        <v>0.4975</v>
       </c>
       <c r="G125" t="n">
-        <v>15.6321</v>
+        <v>27.2712</v>
       </c>
       <c r="H125" t="n">
-        <v>43.6614</v>
+        <v>46.5554</v>
       </c>
     </row>
     <row r="126">
@@ -4442,20 +4442,20 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.9374</v>
+        <v>0.956</v>
       </c>
       <c r="F126" t="n">
-        <v>1.4095</v>
+        <v>0.571</v>
       </c>
       <c r="G126" t="n">
-        <v>23.8029</v>
+        <v>20.5654</v>
       </c>
       <c r="H126" t="n">
-        <v>41.9383</v>
+        <v>43.0163</v>
       </c>
     </row>
     <row r="127">
@@ -4474,20 +4474,20 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.8128</v>
+        <v>0.8288</v>
       </c>
       <c r="F127" t="n">
-        <v>1.8364</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="G127" t="n">
-        <v>41.2129</v>
+        <v>40.4072</v>
       </c>
       <c r="H127" t="n">
-        <v>59.9333</v>
+        <v>62.5715</v>
       </c>
     </row>
     <row r="128">
@@ -4510,16 +4510,16 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.9598</v>
+        <v>0.9595</v>
       </c>
       <c r="F128" t="n">
-        <v>1.4065</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="G128" t="n">
-        <v>19.6326</v>
+        <v>19.8725</v>
       </c>
       <c r="H128" t="n">
-        <v>41.7819</v>
+        <v>43.5155</v>
       </c>
     </row>
     <row r="129">
@@ -4538,20 +4538,20 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.968</v>
+        <v>0.9586</v>
       </c>
       <c r="F129" t="n">
-        <v>1.4073</v>
+        <v>0.5618</v>
       </c>
       <c r="G129" t="n">
-        <v>17.451</v>
+        <v>19.9911</v>
       </c>
       <c r="H129" t="n">
-        <v>41.8212</v>
+        <v>43.477</v>
       </c>
     </row>
     <row r="130">
@@ -4574,16 +4574,16 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>0.9613</v>
+        <v>0.9603</v>
       </c>
       <c r="F130" t="n">
-        <v>1.4074</v>
+        <v>0.5623</v>
       </c>
       <c r="G130" t="n">
-        <v>19.4069</v>
+        <v>19.6957</v>
       </c>
       <c r="H130" t="n">
-        <v>41.8309</v>
+        <v>43.4534</v>
       </c>
     </row>
     <row r="131">
@@ -4602,20 +4602,20 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>0.9613</v>
+        <v>0.9574</v>
       </c>
       <c r="F131" t="n">
-        <v>1.4031</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G131" t="n">
-        <v>19.4316</v>
+        <v>20.2078</v>
       </c>
       <c r="H131" t="n">
-        <v>41.6089</v>
+        <v>43.319</v>
       </c>
     </row>
     <row r="132">
@@ -4634,20 +4634,20 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>0.9684</v>
+        <v>0.977</v>
       </c>
       <c r="F132" t="n">
-        <v>1.4044</v>
+        <v>0.5641</v>
       </c>
       <c r="G132" t="n">
-        <v>17.3323</v>
+        <v>15.7003</v>
       </c>
       <c r="H132" t="n">
-        <v>41.6724</v>
+        <v>43.3598</v>
       </c>
     </row>
     <row r="133">
@@ -4666,20 +4666,20 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>0.9686</v>
+        <v>0.9598</v>
       </c>
       <c r="F133" t="n">
-        <v>1.4066</v>
+        <v>0.5632</v>
       </c>
       <c r="G133" t="n">
-        <v>17.3021</v>
+        <v>19.8599</v>
       </c>
       <c r="H133" t="n">
-        <v>41.7896</v>
+        <v>43.4063</v>
       </c>
     </row>
     <row r="134">
@@ -4698,20 +4698,20 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>0.9797</v>
+        <v>0.9596</v>
       </c>
       <c r="F134" t="n">
-        <v>1.4057</v>
+        <v>0.5628</v>
       </c>
       <c r="G134" t="n">
-        <v>14.6209</v>
+        <v>19.911</v>
       </c>
       <c r="H134" t="n">
-        <v>41.7437</v>
+        <v>43.4284</v>
       </c>
     </row>
     <row r="135">
@@ -4730,20 +4730,20 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>0.96</v>
+        <v>0.977</v>
       </c>
       <c r="F135" t="n">
-        <v>1.406</v>
+        <v>0.5627</v>
       </c>
       <c r="G135" t="n">
-        <v>19.5844</v>
+        <v>15.6884</v>
       </c>
       <c r="H135" t="n">
-        <v>41.7565</v>
+        <v>43.429</v>
       </c>
     </row>
     <row r="136">
@@ -4762,20 +4762,20 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>0.968</v>
+        <v>0.9597</v>
       </c>
       <c r="F136" t="n">
-        <v>1.404</v>
+        <v>0.5623</v>
       </c>
       <c r="G136" t="n">
-        <v>17.4409</v>
+        <v>19.8686</v>
       </c>
       <c r="H136" t="n">
-        <v>41.6549</v>
+        <v>43.4517</v>
       </c>
     </row>
     <row r="137">
@@ -4794,20 +4794,20 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>0.9757</v>
+        <v>0.9668</v>
       </c>
       <c r="F137" t="n">
-        <v>1.3586</v>
+        <v>0.6133</v>
       </c>
       <c r="G137" t="n">
-        <v>15.276</v>
+        <v>18.2103</v>
       </c>
       <c r="H137" t="n">
-        <v>39.2445</v>
+        <v>40.8423</v>
       </c>
     </row>
     <row r="138">
@@ -4826,20 +4826,20 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>0.9761</v>
+        <v>0.9143</v>
       </c>
       <c r="F138" t="n">
-        <v>1.3648</v>
+        <v>0.6056</v>
       </c>
       <c r="G138" t="n">
-        <v>15.6221</v>
+        <v>27.5488</v>
       </c>
       <c r="H138" t="n">
-        <v>39.5832</v>
+        <v>41.2449</v>
       </c>
     </row>
     <row r="139">
@@ -4862,16 +4862,16 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.9281</v>
       </c>
       <c r="F139" t="n">
-        <v>1.3662</v>
+        <v>0.6077</v>
       </c>
       <c r="G139" t="n">
-        <v>24.931</v>
+        <v>25.2637</v>
       </c>
       <c r="H139" t="n">
-        <v>39.6549</v>
+        <v>41.1364</v>
       </c>
     </row>
     <row r="140">
@@ -4890,20 +4890,20 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>0.9472</v>
+        <v>0.9653</v>
       </c>
       <c r="F140" t="n">
-        <v>1.3613</v>
+        <v>0.6055</v>
       </c>
       <c r="G140" t="n">
-        <v>22.3945</v>
+        <v>18.9847</v>
       </c>
       <c r="H140" t="n">
-        <v>39.3913</v>
+        <v>41.2521</v>
       </c>
     </row>
     <row r="141">
@@ -4922,20 +4922,20 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>0.9298</v>
+        <v>0.928</v>
       </c>
       <c r="F141" t="n">
-        <v>1.37</v>
+        <v>0.5896</v>
       </c>
       <c r="G141" t="n">
-        <v>25.806</v>
+        <v>26.1671</v>
       </c>
       <c r="H141" t="n">
-        <v>39.8611</v>
+        <v>42.0727</v>
       </c>
     </row>
     <row r="142">
@@ -4954,20 +4954,20 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>0.9761</v>
+        <v>0.9143</v>
       </c>
       <c r="F142" t="n">
-        <v>1.3648</v>
+        <v>0.6056</v>
       </c>
       <c r="G142" t="n">
-        <v>15.6221</v>
+        <v>27.5488</v>
       </c>
       <c r="H142" t="n">
-        <v>39.5832</v>
+        <v>41.2449</v>
       </c>
     </row>
     <row r="143">
@@ -4990,16 +4990,16 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>0.9313</v>
+        <v>0.9283</v>
       </c>
       <c r="F143" t="n">
-        <v>1.3665</v>
+        <v>0.6083</v>
       </c>
       <c r="G143" t="n">
-        <v>24.4046</v>
+        <v>25.2739</v>
       </c>
       <c r="H143" t="n">
-        <v>39.6758</v>
+        <v>41.1037</v>
       </c>
     </row>
     <row r="144">
@@ -5018,20 +5018,20 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>0.9313</v>
+        <v>0.905</v>
       </c>
       <c r="F144" t="n">
-        <v>1.3682</v>
+        <v>0.6028</v>
       </c>
       <c r="G144" t="n">
-        <v>24.4502</v>
+        <v>28.815</v>
       </c>
       <c r="H144" t="n">
-        <v>39.7665</v>
+        <v>41.3898</v>
       </c>
     </row>
     <row r="145">
@@ -5050,20 +5050,20 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>0.9298</v>
+        <v>0.928</v>
       </c>
       <c r="F145" t="n">
-        <v>1.37</v>
+        <v>0.5896</v>
       </c>
       <c r="G145" t="n">
-        <v>25.806</v>
+        <v>26.1671</v>
       </c>
       <c r="H145" t="n">
-        <v>39.8611</v>
+        <v>42.0727</v>
       </c>
     </row>
     <row r="146">
@@ -5082,20 +5082,20 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>0.8117</v>
+        <v>0.8262</v>
       </c>
       <c r="F146" t="n">
-        <v>1.8337</v>
+        <v>0.0936</v>
       </c>
       <c r="G146" t="n">
-        <v>41.2649</v>
+        <v>40.5722</v>
       </c>
       <c r="H146" t="n">
-        <v>59.8362</v>
+        <v>62.5293</v>
       </c>
     </row>
     <row r="147">
@@ -5114,20 +5114,20 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>0.8117</v>
+        <v>0.8255</v>
       </c>
       <c r="F147" t="n">
-        <v>1.8329</v>
+        <v>0.0946</v>
       </c>
       <c r="G147" t="n">
-        <v>41.2352</v>
+        <v>40.6409</v>
       </c>
       <c r="H147" t="n">
-        <v>59.8089</v>
+        <v>62.4928</v>
       </c>
     </row>
     <row r="148">
@@ -5146,20 +5146,20 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>0.8117</v>
+        <v>0.8296</v>
       </c>
       <c r="F148" t="n">
-        <v>1.8345</v>
+        <v>0.0963</v>
       </c>
       <c r="G148" t="n">
-        <v>41.1723</v>
+        <v>40.4216</v>
       </c>
       <c r="H148" t="n">
-        <v>59.8646</v>
+        <v>62.4358</v>
       </c>
     </row>
     <row r="149">
@@ -5178,20 +5178,20 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>0.8129</v>
+        <v>0.8267</v>
       </c>
       <c r="F149" t="n">
-        <v>1.8352</v>
+        <v>0.0954</v>
       </c>
       <c r="G149" t="n">
-        <v>41.0549</v>
+        <v>40.6111</v>
       </c>
       <c r="H149" t="n">
-        <v>59.8899</v>
+        <v>62.4676</v>
       </c>
     </row>
     <row r="150">
@@ -5210,20 +5210,20 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>0.8131</v>
+        <v>0.8315</v>
       </c>
       <c r="F150" t="n">
-        <v>1.8369</v>
+        <v>0.0941</v>
       </c>
       <c r="G150" t="n">
-        <v>41.1718</v>
+        <v>40.2277</v>
       </c>
       <c r="H150" t="n">
-        <v>59.9506</v>
+        <v>62.5092</v>
       </c>
     </row>
     <row r="151">
@@ -5242,20 +5242,20 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>0.8131</v>
+        <v>0.8306</v>
       </c>
       <c r="F151" t="n">
-        <v>1.8358</v>
+        <v>0.0958</v>
       </c>
       <c r="G151" t="n">
-        <v>41.1741</v>
+        <v>40.4095</v>
       </c>
       <c r="H151" t="n">
-        <v>59.9109</v>
+        <v>62.4518</v>
       </c>
     </row>
     <row r="152">
@@ -5274,20 +5274,20 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>0.8147</v>
+        <v>0.8306</v>
       </c>
       <c r="F152" t="n">
-        <v>1.8367</v>
+        <v>0.098</v>
       </c>
       <c r="G152" t="n">
-        <v>41.086</v>
+        <v>40.3252</v>
       </c>
       <c r="H152" t="n">
-        <v>59.9441</v>
+        <v>62.3771</v>
       </c>
     </row>
     <row r="153">
@@ -5310,16 +5310,16 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.7945</v>
       </c>
       <c r="F153" t="n">
-        <v>1.8368</v>
+        <v>0.091</v>
       </c>
       <c r="G153" t="n">
-        <v>41.1103</v>
+        <v>43.169</v>
       </c>
       <c r="H153" t="n">
-        <v>59.9469</v>
+        <v>62.6162</v>
       </c>
     </row>
     <row r="154">
@@ -5338,20 +5338,20 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>0.8106</v>
+        <v>0.8244</v>
       </c>
       <c r="F154" t="n">
-        <v>1.8392</v>
+        <v>0.0983</v>
       </c>
       <c r="G154" t="n">
-        <v>41.3209</v>
+        <v>40.666</v>
       </c>
       <c r="H154" t="n">
-        <v>60.0346</v>
+        <v>62.3642</v>
       </c>
     </row>
     <row r="155">
@@ -5370,20 +5370,20 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>0.8310999999999999</v>
+        <v>0.8474</v>
       </c>
       <c r="F155" t="n">
-        <v>1.8014</v>
+        <v>0.12</v>
       </c>
       <c r="G155" t="n">
-        <v>39.6303</v>
+        <v>38.9302</v>
       </c>
       <c r="H155" t="n">
-        <v>58.6658</v>
+        <v>61.6123</v>
       </c>
     </row>
     <row r="156">
@@ -5406,16 +5406,16 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>0.8331</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="F156" t="n">
-        <v>1.8078</v>
+        <v>0.1101</v>
       </c>
       <c r="G156" t="n">
-        <v>39.4958</v>
+        <v>41.4233</v>
       </c>
       <c r="H156" t="n">
-        <v>58.8995</v>
+        <v>61.9566</v>
       </c>
     </row>
     <row r="157">
@@ -5438,16 +5438,16 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>0.8336</v>
+        <v>0.8161</v>
       </c>
       <c r="F157" t="n">
-        <v>1.8116</v>
+        <v>0.1064</v>
       </c>
       <c r="G157" t="n">
-        <v>39.3823</v>
+        <v>41.3924</v>
       </c>
       <c r="H157" t="n">
-        <v>59.0369</v>
+        <v>62.086</v>
       </c>
     </row>
     <row r="158">
@@ -5470,16 +5470,16 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>0.8366</v>
+        <v>0.8215</v>
       </c>
       <c r="F158" t="n">
-        <v>1.7551</v>
+        <v>0.1677</v>
       </c>
       <c r="G158" t="n">
-        <v>39.4645</v>
+        <v>41.0337</v>
       </c>
       <c r="H158" t="n">
-        <v>56.9446</v>
+        <v>59.9177</v>
       </c>
     </row>
     <row r="159">
@@ -5498,20 +5498,20 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>0.9736</v>
+        <v>0.9598</v>
       </c>
       <c r="F159" t="n">
-        <v>1.421</v>
+        <v>0.5425</v>
       </c>
       <c r="G159" t="n">
-        <v>16.0301</v>
+        <v>19.8307</v>
       </c>
       <c r="H159" t="n">
-        <v>42.5221</v>
+        <v>44.4211</v>
       </c>
     </row>
     <row r="160">
@@ -5530,20 +5530,20 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 300, 'min_samples_split': 10, 'min_samples_leaf': 1, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>0.8164</v>
+        <v>0.8535</v>
       </c>
       <c r="F160" t="n">
-        <v>1.809</v>
+        <v>0.1142</v>
       </c>
       <c r="G160" t="n">
-        <v>40.775</v>
+        <v>38.3087</v>
       </c>
       <c r="H160" t="n">
-        <v>58.9446</v>
+        <v>61.8129</v>
       </c>
     </row>
     <row r="161">
@@ -5562,20 +5562,20 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 10, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>0.8146</v>
+        <v>0.8255</v>
       </c>
       <c r="F161" t="n">
-        <v>1.8098</v>
+        <v>0.1117</v>
       </c>
       <c r="G161" t="n">
-        <v>40.8601</v>
+        <v>40.2414</v>
       </c>
       <c r="H161" t="n">
-        <v>58.9743</v>
+        <v>61.9008</v>
       </c>
     </row>
     <row r="162">
@@ -5594,20 +5594,20 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>0.9752</v>
+        <v>0.9588</v>
       </c>
       <c r="F162" t="n">
-        <v>1.4268</v>
+        <v>0.5386</v>
       </c>
       <c r="G162" t="n">
-        <v>15.5208</v>
+        <v>19.8836</v>
       </c>
       <c r="H162" t="n">
-        <v>42.8121</v>
+        <v>44.6132</v>
       </c>
     </row>
     <row r="163">
@@ -5626,20 +5626,20 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>0.9386</v>
+        <v>0.9181</v>
       </c>
       <c r="F163" t="n">
-        <v>1.3742</v>
+        <v>0.5947</v>
       </c>
       <c r="G163" t="n">
-        <v>23.2084</v>
+        <v>27.1548</v>
       </c>
       <c r="H163" t="n">
-        <v>40.0892</v>
+        <v>41.8139</v>
       </c>
     </row>
     <row r="164">
@@ -5658,20 +5658,20 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 0.3, 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>0.98</v>
+        <v>0.9653</v>
       </c>
       <c r="F164" t="n">
-        <v>1.3598</v>
+        <v>0.6047</v>
       </c>
       <c r="G164" t="n">
-        <v>14.6251</v>
+        <v>18.982</v>
       </c>
       <c r="H164" t="n">
-        <v>39.3099</v>
+        <v>41.2957</v>
       </c>
     </row>
     <row r="165">
@@ -5690,20 +5690,20 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 1, 'max_features': 'sqrt', 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': None}</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>0.9766</v>
+        <v>0.9164</v>
       </c>
       <c r="F165" t="n">
-        <v>1.4439</v>
+        <v>0.4975</v>
       </c>
       <c r="G165" t="n">
-        <v>15.6321</v>
+        <v>27.2712</v>
       </c>
       <c r="H165" t="n">
-        <v>43.6614</v>
+        <v>46.5554</v>
       </c>
     </row>
     <row r="166">
@@ -5722,20 +5722,20 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>{'n_estimators': 300, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>0.8994</v>
+        <v>0.8807</v>
       </c>
       <c r="F166" t="n">
-        <v>2.0873</v>
+        <v>-0.0871</v>
       </c>
       <c r="G166" t="n">
-        <v>34.6214</v>
+        <v>36.8214</v>
       </c>
       <c r="H166" t="n">
-        <v>68.3343</v>
+        <v>68.4791</v>
       </c>
     </row>
     <row r="167">
@@ -5754,20 +5754,20 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>0.9317</v>
+        <v>0.9209000000000001</v>
       </c>
       <c r="F167" t="n">
-        <v>1.3668</v>
+        <v>0.5994</v>
       </c>
       <c r="G167" t="n">
-        <v>24.5118</v>
+        <v>26.1518</v>
       </c>
       <c r="H167" t="n">
-        <v>39.6886</v>
+        <v>41.5714</v>
       </c>
     </row>
     <row r="168">
@@ -5790,16 +5790,16 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>0.9391</v>
+        <v>0.9311</v>
       </c>
       <c r="F168" t="n">
-        <v>1.3635</v>
+        <v>0.6088</v>
       </c>
       <c r="G168" t="n">
-        <v>24.3951</v>
+        <v>25.8398</v>
       </c>
       <c r="H168" t="n">
-        <v>39.5112</v>
+        <v>41.0773</v>
       </c>
     </row>
     <row r="169">
@@ -5818,20 +5818,20 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>0.9504</v>
+        <v>0.9418</v>
       </c>
       <c r="F169" t="n">
-        <v>1.3994</v>
+        <v>0.5447</v>
       </c>
       <c r="G169" t="n">
-        <v>21.2894</v>
+        <v>22.8552</v>
       </c>
       <c r="H169" t="n">
-        <v>41.4185</v>
+        <v>44.315</v>
       </c>
     </row>
     <row r="170">
@@ -5850,20 +5850,20 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>{'n_estimators': 500, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 5, 'min_samples_leaf': 2, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>0.9556</v>
+        <v>0.9634</v>
       </c>
       <c r="F170" t="n">
-        <v>1.4349</v>
+        <v>0.5697</v>
       </c>
       <c r="G170" t="n">
-        <v>20.9823</v>
+        <v>19.1851</v>
       </c>
       <c r="H170" t="n">
-        <v>43.2193</v>
+        <v>43.0815</v>
       </c>
     </row>
     <row r="171">
@@ -5882,20 +5882,20 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>0.9444</v>
+        <v>0.9471000000000001</v>
       </c>
       <c r="F171" t="n">
-        <v>1.3842</v>
+        <v>0.6274</v>
       </c>
       <c r="G171" t="n">
-        <v>23.233</v>
+        <v>21.7577</v>
       </c>
       <c r="H171" t="n">
-        <v>40.6209</v>
+        <v>40.0897</v>
       </c>
     </row>
     <row r="172">
@@ -5914,20 +5914,20 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 500, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'log2', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>0.9385</v>
+        <v>0.9166</v>
       </c>
       <c r="F172" t="n">
-        <v>1.3677</v>
+        <v>0.584</v>
       </c>
       <c r="G172" t="n">
-        <v>23.5341</v>
+        <v>27.4273</v>
       </c>
       <c r="H172" t="n">
-        <v>39.738</v>
+        <v>42.3625</v>
       </c>
     </row>
   </sheetData>

--- a/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X9.cis.beta.carotene/RANDOMSEARCH_DETAILS_X9.cis.beta.carotene.xlsx
+++ b/ROSA_vitaSPEC/CLUSTER/random_forest/moyennes/Results/meso_silica/X9.cis.beta.carotene/RANDOMSEARCH_DETAILS_X9.cis.beta.carotene.xlsx
@@ -1466,7 +1466,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 20}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 0.3, 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>{'n_estimators': 200, 'min_samples_split': 2, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': None}</t>
+          <t>{'n_estimators': 200, 'min_samples_split': 5, 'min_samples_leaf': 4, 'max_features': 'sqrt', 'max_depth': 10}</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 10}</t>
+          <t>{'n_estimators': 100, 'min_samples_split': 10, 'min_samples_leaf': 2, 'max_features': 'log2', 'max_depth': 20}</t>
         </is>
       </c>
       <c r="E148" t="n">
@@ -5156,7 +5156,7 @@
         <v>0.0963</v>
       </c>
       <c r="G148" t="n">
-        <v>40.4216</v>
+        <v>40.4223</v>
       </c>
       <c r="H148" t="n">
         <v>62.4358</v>
